--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="88">
   <si>
     <t>#</t>
   </si>
@@ -95,6 +95,15 @@
     <t>SellPrice</t>
   </si>
   <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>MaxDurability</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -165,6 +174,15 @@
   </si>
   <si>
     <t>售价</t>
+  </si>
+  <si>
+    <t>重量(克)</t>
+  </si>
+  <si>
+    <t>最大耐久度</t>
+  </si>
+  <si>
+    <t>稀有度</t>
   </si>
   <si>
     <t>钱包</t>
@@ -285,7 +303,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,148 +766,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1240,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1262,9 +1287,12 @@
     <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="43" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
+    <col min="24" max="24" width="15" customWidth="1"/>
+    <col min="25" max="25" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1291,8 +1319,11 @@
       <c r="T1" s="2"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1357,149 +1388,176 @@
       <c r="V2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:22">
+    <row r="5" ht="15" customHeight="1" spans="1:25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1508,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H5" s="1">
         <v>1901</v>
@@ -1538,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
@@ -1547,23 +1605,32 @@
         <v>0</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V5" s="1">
         <v>50</v>
       </c>
+      <c r="W5" s="1">
+        <v>50</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:22">
+    <row r="6" ht="15" customHeight="1" spans="1:25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1572,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H6" s="1">
         <v>1902</v>
@@ -1602,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
@@ -1611,23 +1678,32 @@
         <v>0</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V6" s="1">
         <v>10</v>
       </c>
+      <c r="W6" s="1">
+        <v>100</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:22">
+    <row r="7" ht="15" customHeight="1" spans="1:25">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1636,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H7" s="1">
         <v>1903</v>
@@ -1666,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
@@ -1675,23 +1751,32 @@
         <v>0</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V7" s="1">
         <v>10</v>
       </c>
+      <c r="W7" s="1">
+        <v>100</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:22">
+    <row r="8" ht="15" customHeight="1" spans="1:25">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1700,7 +1785,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1">
         <v>1904</v>
@@ -1730,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -1739,23 +1824,32 @@
         <v>0</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V8" s="1">
         <v>100</v>
       </c>
+      <c r="W8" s="1">
+        <v>200</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:22">
+    <row r="9" ht="15" customHeight="1" spans="1:25">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1764,7 +1858,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H9" s="1">
         <v>1905</v>
@@ -1794,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
@@ -1803,23 +1897,32 @@
         <v>0</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
       </c>
+      <c r="W9" s="1">
+        <v>50</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:22">
+    <row r="10" ht="15" customHeight="1" spans="1:25">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -1828,7 +1931,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H10" s="1">
         <v>1906</v>
@@ -1858,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
@@ -1867,23 +1970,32 @@
         <v>0</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V10" s="1">
         <v>0</v>
       </c>
+      <c r="W10" s="1">
+        <v>30</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:22">
+    <row r="11" ht="15" customHeight="1" spans="1:25">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -1892,7 +2004,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H11" s="1">
         <v>1907</v>
@@ -1922,7 +2034,7 @@
         <v>3001</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R11" s="1">
         <v>0</v>
@@ -1931,23 +2043,32 @@
         <v>0</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
       </c>
+      <c r="W11" s="1">
+        <v>500</v>
+      </c>
+      <c r="X11" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:22">
+    <row r="12" ht="15" customHeight="1" spans="1:25">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -1956,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H12" s="1">
         <v>1908</v>
@@ -1986,7 +2107,7 @@
         <v>3002</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R12" s="1">
         <v>0</v>
@@ -1995,23 +2116,32 @@
         <v>0</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="V12" s="1">
         <v>0</v>
       </c>
+      <c r="W12" s="1">
+        <v>800</v>
+      </c>
+      <c r="X12" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:22">
+    <row r="13" ht="15" customHeight="1" spans="1:25">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -2020,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H13" s="1">
         <v>1909</v>
@@ -2050,7 +2180,7 @@
         <v>3003</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
@@ -2059,23 +2189,32 @@
         <v>0</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="V13" s="1">
         <v>0</v>
       </c>
+      <c r="W13" s="1">
+        <v>600</v>
+      </c>
+      <c r="X13" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:22">
+    <row r="14" ht="15" customHeight="1" spans="1:25">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -2084,7 +2223,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H14" s="1">
         <v>1910</v>
@@ -2114,7 +2253,7 @@
         <v>4001</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="R14" s="1">
         <v>2</v>
@@ -2123,23 +2262,32 @@
         <v>3</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="V14" s="1">
         <v>500</v>
       </c>
+      <c r="W14" s="1">
+        <v>700</v>
+      </c>
+      <c r="X14" s="1">
+        <v>80</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:22">
+    <row r="15" ht="15" customHeight="1" spans="1:25">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -2148,7 +2296,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H15" s="1">
         <v>1911</v>
@@ -2178,7 +2326,7 @@
         <v>4002</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="R15" s="1">
         <v>2</v>
@@ -2187,23 +2335,32 @@
         <v>3</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="V15" s="1">
         <v>500</v>
       </c>
+      <c r="W15" s="1">
+        <v>1200</v>
+      </c>
+      <c r="X15" s="1">
+        <v>80</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:22">
+    <row r="16" ht="15" customHeight="1" spans="1:25">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2212,7 +2369,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H16" s="1">
         <v>1912</v>
@@ -2242,7 +2399,7 @@
         <v>4003</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="R16" s="1">
         <v>1</v>
@@ -2251,13 +2408,22 @@
         <v>2</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="V16" s="1">
         <v>300</v>
+      </c>
+      <c r="W16" s="1">
+        <v>100</v>
+      </c>
+      <c r="X16" s="1">
+        <v>80</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -71,9 +71,6 @@
     <t>CanEquip</t>
   </si>
   <si>
-    <t>EquipType</t>
-  </si>
-  <si>
     <t>SpecialEffectId</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
   </si>
   <si>
     <t>是否可装备</t>
-  </si>
-  <si>
-    <t>装备类型</t>
   </si>
   <si>
     <t>特殊效果ID</t>
@@ -303,14 +297,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,148 +753,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1265,8 +1252,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:X16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1280,19 +1267,18 @@
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="43" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="15" customWidth="1"/>
-    <col min="25" max="25" width="8" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="43" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="15" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1312,18 +1298,17 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1367,19 +1352,19 @@
       <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U2" s="1" t="s">
@@ -1394,170 +1379,161 @@
       <c r="X2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="U3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>25</v>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:25">
+    <row r="5" ht="15" customHeight="1" spans="1:24">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1566,7 +1542,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H5" s="1">
         <v>1901</v>
@@ -1592,45 +1568,42 @@
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>54</v>
+      <c r="P5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
       </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>55</v>
+      <c r="S5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U5" s="1">
+        <v>50</v>
       </c>
       <c r="V5" s="1">
         <v>50</v>
       </c>
       <c r="W5" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:25">
+    <row r="6" ht="15" customHeight="1" spans="1:24">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1639,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H6" s="1">
         <v>1902</v>
@@ -1665,45 +1638,42 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>54</v>
+      <c r="P6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
       </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>55</v>
+      <c r="S6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" s="1">
+        <v>10</v>
       </c>
       <c r="V6" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="W6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:25">
+    <row r="7" ht="15" customHeight="1" spans="1:24">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1712,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H7" s="1">
         <v>1903</v>
@@ -1738,45 +1708,42 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>54</v>
+      <c r="P7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
       </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>55</v>
+      <c r="S7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U7" s="1">
+        <v>10</v>
       </c>
       <c r="V7" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="W7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:25">
+    <row r="8" ht="15" customHeight="1" spans="1:24">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1785,7 +1752,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H8" s="1">
         <v>1904</v>
@@ -1811,45 +1778,42 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>54</v>
+      <c r="P8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
       </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>55</v>
+      <c r="S8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U8" s="1">
+        <v>100</v>
       </c>
       <c r="V8" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W8" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:25">
+    <row r="9" ht="15" customHeight="1" spans="1:24">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1858,7 +1822,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H9" s="1">
         <v>1905</v>
@@ -1884,45 +1848,42 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>54</v>
+      <c r="P9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
       </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>55</v>
+      <c r="S9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
       </c>
       <c r="V9" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W9" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:25">
+    <row r="10" ht="15" customHeight="1" spans="1:24">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -1931,7 +1892,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" s="1">
         <v>1906</v>
@@ -1957,45 +1918,42 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>54</v>
+      <c r="P10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>55</v>
+      <c r="S10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W10" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:25">
+    <row r="11" ht="15" customHeight="1" spans="1:24">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2004,7 +1962,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H11" s="1">
         <v>1907</v>
@@ -2028,47 +1986,44 @@
         <v>1</v>
       </c>
       <c r="O11" s="1">
-        <v>4</v>
-      </c>
-      <c r="P11" s="1">
         <v>3001</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>54</v>
+      <c r="P11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
       </c>
       <c r="R11" s="1">
         <v>0</v>
       </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>69</v>
+      <c r="S11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
       </c>
       <c r="V11" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W11" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="X11" s="1">
-        <v>100</v>
-      </c>
-      <c r="Y11" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:25">
+    <row r="12" ht="15" customHeight="1" spans="1:24">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -2077,7 +2032,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H12" s="1">
         <v>1908</v>
@@ -2101,47 +2056,44 @@
         <v>1</v>
       </c>
       <c r="O12" s="1">
-        <v>4</v>
-      </c>
-      <c r="P12" s="1">
         <v>3002</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>54</v>
+      <c r="P12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
       </c>
       <c r="R12" s="1">
         <v>0</v>
       </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>72</v>
+      <c r="S12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
       </c>
       <c r="V12" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="W12" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="X12" s="1">
-        <v>100</v>
-      </c>
-      <c r="Y12" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:25">
+    <row r="13" ht="15" customHeight="1" spans="1:24">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -2150,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H13" s="1">
         <v>1909</v>
@@ -2174,47 +2126,44 @@
         <v>1</v>
       </c>
       <c r="O13" s="1">
-        <v>4</v>
-      </c>
-      <c r="P13" s="1">
         <v>3003</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>54</v>
+      <c r="P13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>75</v>
+      <c r="S13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
       </c>
       <c r="V13" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="W13" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="X13" s="1">
-        <v>100</v>
-      </c>
-      <c r="Y13" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:25">
+    <row r="14" ht="15" customHeight="1" spans="1:24">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -2223,7 +2172,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1">
         <v>1910</v>
@@ -2247,47 +2196,44 @@
         <v>1</v>
       </c>
       <c r="O14" s="1">
-        <v>1</v>
-      </c>
-      <c r="P14" s="1">
         <v>4001</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>78</v>
+      <c r="P14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>2</v>
       </c>
       <c r="R14" s="1">
-        <v>2</v>
-      </c>
-      <c r="S14" s="1">
         <v>3</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>79</v>
+      <c r="S14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U14" s="1">
+        <v>500</v>
       </c>
       <c r="V14" s="1">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W14" s="1">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="X14" s="1">
-        <v>80</v>
-      </c>
-      <c r="Y14" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:25">
+    <row r="15" ht="15" customHeight="1" spans="1:24">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -2296,7 +2242,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H15" s="1">
         <v>1911</v>
@@ -2320,47 +2266,44 @@
         <v>1</v>
       </c>
       <c r="O15" s="1">
+        <v>4002</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q15" s="1">
         <v>2</v>
       </c>
-      <c r="P15" s="1">
-        <v>4002</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="R15" s="1">
-        <v>2</v>
-      </c>
-      <c r="S15" s="1">
         <v>3</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>83</v>
+      <c r="S15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="1">
+        <v>500</v>
       </c>
       <c r="V15" s="1">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="W15" s="1">
-        <v>1200</v>
+        <v>80</v>
       </c>
       <c r="X15" s="1">
-        <v>80</v>
-      </c>
-      <c r="Y15" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:25">
+    <row r="16" ht="15" customHeight="1" spans="1:24">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2369,7 +2312,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H16" s="1">
         <v>1912</v>
@@ -2393,36 +2336,33 @@
         <v>1</v>
       </c>
       <c r="O16" s="1">
-        <v>3</v>
-      </c>
-      <c r="P16" s="1">
         <v>4003</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>86</v>
+      <c r="P16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>1</v>
       </c>
       <c r="R16" s="1">
-        <v>1</v>
-      </c>
-      <c r="S16" s="1">
         <v>2</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>87</v>
+      <c r="S16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U16" s="1">
+        <v>300</v>
       </c>
       <c r="V16" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="W16" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="X16" s="1">
-        <v>80</v>
-      </c>
-      <c r="Y16" s="1">
         <v>3</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="126">
   <si>
     <t>#</t>
   </si>
@@ -185,9 +185,6 @@
     <t>使用后随机获得100-500金币</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>{}</t>
   </si>
   <si>
@@ -227,9 +224,6 @@
     <t>传说中的三神器之一，蕴含神秘力量</t>
   </si>
   <si>
-    <t>3001</t>
-  </si>
-  <si>
     <t>{"MaxHP":"500","CritRate":"15%"}</t>
   </si>
   <si>
@@ -285,6 +279,132 @@
   </si>
   <si>
     <t>{"MoveSpeed":"15%","Evasion":"10%"}</t>
+  </si>
+  <si>
+    <t>月华玉璧</t>
+  </si>
+  <si>
+    <t>月神赐予的古老玉璧，蕴含月华之力，可反射一切邪恶</t>
+  </si>
+  <si>
+    <t>{"Defense":"400","MagicResist":"25%","CritReduction":"20%"}</t>
+  </si>
+  <si>
+    <t>太阴弦月弓</t>
+  </si>
+  <si>
+    <t>月神的弓，弦如弦月般优雅，箭矢蕴含月光之力</t>
+  </si>
+  <si>
+    <t>{"Attack":"350","CritRate":"25%","Evasion":"15%"}</t>
+  </si>
+  <si>
+    <t>月轮镜</t>
+  </si>
+  <si>
+    <t>月神的镜子，能够照亮黑暗，反射月光</t>
+  </si>
+  <si>
+    <t>{"MagicPower":"300","MagicResist":"30%","Regeneration":"8%"}</t>
+  </si>
+  <si>
+    <t>炎魔之心</t>
+  </si>
+  <si>
+    <t>炎魔的心脏，跳动着永恒的火焰</t>
+  </si>
+  <si>
+    <t>{"MaxHP":"500","LifeSteal":"20%","FireDamage":"30%"}</t>
+  </si>
+  <si>
+    <t>炎魔之冠</t>
+  </si>
+  <si>
+    <t>炎魔的王冠，象征权力与统治</t>
+  </si>
+  <si>
+    <t>{"Attack":"400","CritDamage":"50%","Leadership":"15%"}</t>
+  </si>
+  <si>
+    <t>炎魔之剑</t>
+  </si>
+  <si>
+    <t>炎魔的剑，剑身燃烧着永恒的火焰</t>
+  </si>
+  <si>
+    <t>{"Attack":"380","FireDamage":"25%","AttackSpeed":"15%"}</t>
+  </si>
+  <si>
+    <t>古剑·樱花落</t>
+  </si>
+  <si>
+    <t>樱花盛开时锻造的古剑，剑身如樱花般优雅，却有致命的锋芒</t>
+  </si>
+  <si>
+    <t>2007,2008</t>
+  </si>
+  <si>
+    <t>{"Attack":"150","CritRate":"20%","Evasion":"8%"}</t>
+  </si>
+  <si>
+    <t>暗影斗篷</t>
+  </si>
+  <si>
+    <t>用暗影魔法编织的斗篷，能够隐匿身形，融入黑暗</t>
+  </si>
+  <si>
+    <t>2009,2010</t>
+  </si>
+  <si>
+    <t>{"Defense":"80","Evasion":"15%","MagicResist":"15%"}</t>
+  </si>
+  <si>
+    <t>圣光铠甲</t>
+  </si>
+  <si>
+    <t>被圣光祝福的铠甲，闪烁着神圣的光芒，能够保护穿戴者免受邪恶</t>
+  </si>
+  <si>
+    <t>2011,2012</t>
+  </si>
+  <si>
+    <t>{"Defense":"200","MagicResist":"30%","HealthRegen":"3%"}</t>
+  </si>
+  <si>
+    <t>古墓盗贼手套</t>
+  </si>
+  <si>
+    <t>从古墓中发现的神秘手套，能够增强手指的灵活性和力量</t>
+  </si>
+  <si>
+    <t>2013,2014</t>
+  </si>
+  <si>
+    <t>{"Attack":"80","AttackSpeed":"15%","CritRate":"10%"}</t>
+  </si>
+  <si>
+    <t>冰晶靴</t>
+  </si>
+  <si>
+    <t>用冰晶魔法制成的靴子，能够在冰面上快速移动，冻结敌人</t>
+  </si>
+  <si>
+    <t>2015,2016</t>
+  </si>
+  <si>
+    <t>{"MoveSpeed":"20%","Defense":"60","CooldownReduction":"10%"}</t>
+  </si>
+  <si>
+    <t>风暴法杖</t>
+  </si>
+  <si>
+    <t>由风元素凝聚而成的法杖，顶端闪烁着雷电光芒，能够召唤风暴之力</t>
+  </si>
+  <si>
+    <t>2017,2018</t>
+  </si>
+  <si>
+    <t>{"MagicPower":"200","CooldownReduction":"15%","AttackSpeed":"10%"}</t>
   </si>
 </sst>
 </file>
@@ -898,13 +1018,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1252,15 +1375,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:X28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="7" max="7" width="68.1111111111111" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
@@ -1271,7 +1394,7 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="43" customWidth="1"/>
+    <col min="20" max="20" width="68.1111111111111" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
     <col min="22" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
@@ -1528,842 +1651,1670 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:24">
       <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="3">
         <v>1901</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
         <v>99</v>
       </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3">
         <v>1001</v>
       </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="s">
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U5" s="1">
+      <c r="U5" s="3">
         <v>50</v>
       </c>
-      <c r="V5" s="1">
+      <c r="V5" s="3">
         <v>50</v>
       </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1">
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:24">
       <c r="A6" s="1"/>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="H6" s="3">
         <v>1902</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
         <v>99</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
         <v>1002</v>
       </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="s">
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U6" s="1">
+      <c r="U6" s="3">
         <v>10</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V6" s="3">
         <v>100</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:24">
       <c r="A7" s="1"/>
-      <c r="B7" s="1">
+      <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="H7" s="3">
         <v>1903</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
         <v>99</v>
       </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
         <v>1003</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="s">
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U7" s="1">
+      <c r="U7" s="3">
         <v>10</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V7" s="3">
         <v>100</v>
       </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:24">
       <c r="A8" s="1"/>
-      <c r="B8" s="1">
+      <c r="B8" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="H8" s="3">
         <v>1904</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
         <v>20</v>
       </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
         <v>1004</v>
       </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U8" s="1">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="1">
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:24">
       <c r="A9" s="1"/>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="H9" s="3">
         <v>1905</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="s">
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
-      <c r="V9" s="1">
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>50</v>
       </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-      <c r="X9" s="1">
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:24">
       <c r="A10" s="1"/>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="H10" s="3">
         <v>1906</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="s">
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
-      <c r="V10" s="1">
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>30</v>
       </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1">
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:24">
       <c r="A11" s="1"/>
-      <c r="B11" s="1">
+      <c r="B11" s="3">
         <v>7</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1">
-        <v>5</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="3">
+        <v>1907</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
+        <v>3001</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>3001</v>
+      </c>
+      <c r="T11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="1">
-        <v>1907</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1">
-        <v>3001</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
         <v>500</v>
       </c>
-      <c r="W11" s="1">
-        <v>100</v>
-      </c>
-      <c r="X11" s="1">
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:24">
       <c r="A12" s="1"/>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
         <v>8</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1908</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3002</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>3001</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="1">
-        <v>3</v>
-      </c>
-      <c r="F12" s="1">
-        <v>5</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1908</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>3002</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="1">
-        <v>100</v>
-      </c>
-      <c r="X12" s="1">
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:24">
       <c r="A13" s="1"/>
-      <c r="B13" s="1">
+      <c r="B13" s="3">
         <v>9</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1909</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>1</v>
+      </c>
+      <c r="O13" s="3">
+        <v>3003</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>3001</v>
+      </c>
+      <c r="T13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="1">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1909</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>3003</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U13" s="1">
-        <v>0</v>
-      </c>
-      <c r="V13" s="1">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
         <v>600</v>
       </c>
-      <c r="W13" s="1">
-        <v>100</v>
-      </c>
-      <c r="X13" s="1">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:24">
       <c r="A14" s="1"/>
-      <c r="B14" s="1">
+      <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1910</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1</v>
+      </c>
+      <c r="O14" s="3">
+        <v>4001</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="1">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1">
-        <v>4</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="Q14" s="3">
+        <v>2</v>
+      </c>
+      <c r="R14" s="3">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H14" s="1">
-        <v>1910</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
-        <v>4001</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>2</v>
-      </c>
-      <c r="R14" s="1">
-        <v>3</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="U14" s="1">
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="1">
+      <c r="V14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="1">
-        <v>80</v>
-      </c>
-      <c r="X14" s="1">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:24">
       <c r="A15" s="1"/>
-      <c r="B15" s="1">
+      <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1911</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1</v>
+      </c>
+      <c r="O15" s="3">
+        <v>4002</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="1">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="Q15" s="3">
+        <v>2</v>
+      </c>
+      <c r="R15" s="3">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="1">
-        <v>1911</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1">
-        <v>4002</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>2</v>
-      </c>
-      <c r="R15" s="1">
-        <v>3</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="U15" s="1">
+      <c r="U15" s="3">
         <v>500</v>
       </c>
-      <c r="V15" s="1">
+      <c r="V15" s="3">
         <v>1200</v>
       </c>
-      <c r="W15" s="1">
-        <v>80</v>
-      </c>
-      <c r="X15" s="1">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:24">
       <c r="A16" s="1"/>
-      <c r="B16" s="1">
+      <c r="B16" s="3">
         <v>12</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1912</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3">
+        <v>4003</v>
+      </c>
+      <c r="P16" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="1">
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="U16" s="3">
+        <v>300</v>
+      </c>
+      <c r="V16" s="3">
+        <v>100</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24">
+      <c r="B17" s="3">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1913</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5001</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>5001</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>500</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24">
+      <c r="B18" s="3">
+        <v>14</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1914</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5002</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>5001</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>800</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24">
+      <c r="B19" s="3">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3</v>
+      </c>
+      <c r="F19" s="3">
+        <v>5</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1915</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1</v>
+      </c>
+      <c r="O19" s="3">
+        <v>5003</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3">
+        <v>5001</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3">
+        <v>600</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24">
+      <c r="B20" s="3">
+        <v>16</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1916</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3">
+        <v>5004</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>5002</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>500</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24">
+      <c r="B21" s="3">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1917</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1</v>
+      </c>
+      <c r="O21" s="3">
+        <v>5005</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
+        <v>5002</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <v>800</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24">
+      <c r="B22" s="3">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1918</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3">
+        <v>5006</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>5002</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>700</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24">
+      <c r="B23" s="3">
+        <v>19</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="3">
         <v>4</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F23" s="3">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1919</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>1</v>
+      </c>
+      <c r="O23" s="3">
+        <v>6001</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>2</v>
+      </c>
+      <c r="R23" s="3">
         <v>3</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1912</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>1</v>
-      </c>
-      <c r="O16" s="1">
-        <v>4003</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>1</v>
-      </c>
-      <c r="R16" s="1">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="U23" s="3">
+        <v>600</v>
+      </c>
+      <c r="V23" s="3">
+        <v>700</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24">
+      <c r="B24" s="3">
+        <v>20</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1920</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1</v>
+      </c>
+      <c r="O24" s="3">
+        <v>6002</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q24" s="3">
         <v>2</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="U16" s="1">
+      <c r="R24" s="3">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="U24" s="3">
+        <v>400</v>
+      </c>
+      <c r="V24" s="3">
+        <v>500</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24">
+      <c r="B25" s="3">
+        <v>21</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>4</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1921</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3">
+        <v>6003</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>2</v>
+      </c>
+      <c r="R25" s="3">
+        <v>3</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="U25" s="3">
+        <v>600</v>
+      </c>
+      <c r="V25" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24">
+      <c r="B26" s="3">
+        <v>22</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1922</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3">
+        <v>6004</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>2</v>
+      </c>
+      <c r="R26" s="3">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" s="3">
+        <v>400</v>
+      </c>
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V16" s="1">
-        <v>100</v>
-      </c>
-      <c r="W16" s="1">
-        <v>80</v>
-      </c>
-      <c r="X16" s="1">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24">
+      <c r="B27" s="3">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1923</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>1</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3">
+        <v>6005</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>2</v>
+      </c>
+      <c r="R27" s="3">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="U27" s="3">
+        <v>400</v>
+      </c>
+      <c r="V27" s="3">
+        <v>400</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24">
+      <c r="B28" s="3">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" s="3">
+        <v>4</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1924</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>1</v>
+      </c>
+      <c r="O28" s="3">
+        <v>6006</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>2</v>
+      </c>
+      <c r="R28" s="3">
+        <v>3</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U28" s="3">
+        <v>600</v>
+      </c>
+      <c r="V28" s="3">
+        <v>600</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1376,14 +1376,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="68.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="68.1083333333333" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
@@ -1394,7 +1394,7 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="68.1111111111111" customWidth="1"/>
+    <col min="20" max="20" width="68.1083333333333" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
     <col min="22" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="136">
   <si>
     <t>#</t>
   </si>
@@ -185,6 +185,9 @@
     <t>使用后随机获得100-500金币</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>{}</t>
   </si>
   <si>
@@ -224,6 +227,9 @@
     <t>传说中的三神器之一，蕴含神秘力量</t>
   </si>
   <si>
+    <t>3001</t>
+  </si>
+  <si>
     <t>{"MaxHP":"500","CritRate":"15%"}</t>
   </si>
   <si>
@@ -287,6 +293,9 @@
     <t>月神赐予的古老玉璧，蕴含月华之力，可反射一切邪恶</t>
   </si>
   <si>
+    <t>5001</t>
+  </si>
+  <si>
     <t>{"Defense":"400","MagicResist":"25%","CritReduction":"20%"}</t>
   </si>
   <si>
@@ -314,6 +323,9 @@
     <t>炎魔的心脏，跳动着永恒的火焰</t>
   </si>
   <si>
+    <t>5002</t>
+  </si>
+  <si>
     <t>{"MaxHP":"500","LifeSteal":"20%","FireDamage":"30%"}</t>
   </si>
   <si>
@@ -405,6 +417,24 @@
   </si>
   <si>
     <t>{"MagicPower":"200","CooldownReduction":"15%","AttackSpeed":"10%"}</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>游戏中的基础货币</t>
+  </si>
+  <si>
+    <t>起源石</t>
+  </si>
+  <si>
+    <t>高级货币，用于商店购买高级物品</t>
+  </si>
+  <si>
+    <t>灵石</t>
+  </si>
+  <si>
+    <t>战斗资源，用于棋子进阶</t>
   </si>
 </sst>
 </file>
@@ -417,7 +447,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -873,161 +910,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1375,15 +1409,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:X31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="68.1083333333333" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
@@ -1394,7 +1428,7 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="68.1083333333333" customWidth="1"/>
+    <col min="20" max="20" width="50" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
     <col min="22" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
@@ -1651,1670 +1685,1892 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:24">
       <c r="A5" s="1"/>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
         <v>2</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
         <v>1901</v>
       </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
         <v>99</v>
       </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
         <v>1001</v>
       </c>
-      <c r="N5" s="3">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3" t="s">
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="3">
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U5" s="1">
         <v>50</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="1">
         <v>50</v>
       </c>
-      <c r="W5" s="3">
-        <v>0</v>
-      </c>
-      <c r="X5" s="3">
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:24">
       <c r="A6" s="1"/>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1902</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>99</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1902</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>99</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1002</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U6" s="3">
+      <c r="U6" s="1">
         <v>10</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="1">
         <v>100</v>
       </c>
-      <c r="W6" s="3">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3">
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:24">
       <c r="A7" s="1"/>
-      <c r="B7" s="3">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="3">
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="1">
         <v>1903</v>
       </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3">
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
         <v>99</v>
       </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
         <v>1003</v>
       </c>
-      <c r="N7" s="3">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="s">
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="3">
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U7" s="1">
         <v>10</v>
       </c>
-      <c r="V7" s="3">
+      <c r="V7" s="1">
         <v>100</v>
       </c>
-      <c r="W7" s="3">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3">
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:24">
       <c r="A8" s="1"/>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="1">
         <v>1904</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
         <v>20</v>
       </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
         <v>1004</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="s">
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U8" s="1">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="1">
         <v>200</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:24">
       <c r="A9" s="1"/>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="1">
         <v>1905</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="s">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
         <v>50</v>
       </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:24">
       <c r="A10" s="1"/>
-      <c r="B10" s="3">
+      <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <v>4</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="G10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="1">
         <v>1906</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="s">
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
         <v>30</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:24">
       <c r="A11" s="1"/>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1">
         <v>3</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="1">
         <v>5</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="G11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="1">
         <v>1907</v>
       </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1</v>
-      </c>
-      <c r="O11" s="3">
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
         <v>3001</v>
       </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0</v>
-      </c>
-      <c r="S11" s="3">
-        <v>3001</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3">
+      <c r="P11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
         <v>500</v>
       </c>
-      <c r="W11" s="3">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3">
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:24">
       <c r="A12" s="1"/>
-      <c r="B12" s="3">
+      <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1908</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>3002</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="3">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1908</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3002</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>3001</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
+      <c r="T12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:24">
       <c r="A13" s="1"/>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="1">
         <v>3</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="1">
         <v>5</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="3">
+      <c r="G13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="1">
         <v>1909</v>
       </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1</v>
-      </c>
-      <c r="O13" s="3">
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
         <v>3003</v>
       </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3">
-        <v>0</v>
-      </c>
-      <c r="S13" s="3">
-        <v>3001</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
+      <c r="P13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
         <v>600</v>
       </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:24">
       <c r="A14" s="1"/>
-      <c r="B14" s="3">
+      <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <v>4</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="1">
         <v>1910</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
         <v>4001</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="P14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="1">
         <v>2</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="1">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="S14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U14" s="1">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="1">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:24">
       <c r="A15" s="1"/>
-      <c r="B15" s="3">
+      <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1">
         <v>4</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="1">
         <v>4</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="G15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="1">
         <v>1911</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
         <v>4002</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="P15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q15" s="1">
         <v>2</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="1">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="S15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="1">
         <v>500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="1">
         <v>1200</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:24">
       <c r="A16" s="1"/>
-      <c r="B16" s="3">
+      <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="1">
         <v>4</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="1">
         <v>3</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="G16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="1">
         <v>1912</v>
       </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3">
-        <v>1</v>
-      </c>
-      <c r="O16" s="3">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
         <v>4003</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3">
+      <c r="P16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
         <v>2</v>
       </c>
-      <c r="S16" s="3">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U16" s="3">
+      <c r="S16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U16" s="1">
         <v>300</v>
       </c>
-      <c r="V16" s="3">
+      <c r="V16" s="1">
         <v>100</v>
       </c>
-      <c r="W16" s="3">
-        <v>0</v>
-      </c>
-      <c r="X16" s="3">
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:24">
-      <c r="B17" s="3">
+    <row r="17" ht="15" customHeight="1" spans="1:24">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="1">
         <v>3</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="1">
         <v>5</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="G17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="1">
         <v>1913</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1">
         <v>5001</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
-        <v>5001</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="P17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:24">
-      <c r="B18" s="3">
+    <row r="18" ht="15" customHeight="1" spans="1:24">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="1">
         <v>3</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="1">
         <v>5</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1914</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1">
+        <v>5002</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="3">
-        <v>1914</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>1</v>
-      </c>
-      <c r="O18" s="3">
-        <v>5002</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
-        <v>5001</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="T18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
         <v>800</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:24">
-      <c r="B19" s="3">
+    <row r="19" ht="15" customHeight="1" spans="1:24">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="1">
         <v>3</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="1">
         <v>5</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="3">
+      <c r="G19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="1">
         <v>1915</v>
       </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
-        <v>1</v>
-      </c>
-      <c r="O19" s="3">
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1">
         <v>5003</v>
       </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0</v>
-      </c>
-      <c r="S19" s="3">
-        <v>5001</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="U19" s="3">
-        <v>0</v>
-      </c>
-      <c r="V19" s="3">
+      <c r="P19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
         <v>600</v>
       </c>
-      <c r="W19" s="3">
-        <v>0</v>
-      </c>
-      <c r="X19" s="3">
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:24">
-      <c r="B20" s="3">
+    <row r="20" ht="15" customHeight="1" spans="1:24">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
         <v>16</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="1">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="1">
         <v>5</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="1">
         <v>1916</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1">
         <v>5004</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>5002</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="P20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="U20" s="1">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:24">
-      <c r="B21" s="3">
+    <row r="21" ht="15" customHeight="1" spans="1:24">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1">
         <v>3</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="1">
         <v>5</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="G21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" s="1">
         <v>1917</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1">
         <v>5005</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
-        <v>5002</v>
-      </c>
-      <c r="T21" s="3" t="s">
+      <c r="P21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="T21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
         <v>800</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="W21" s="1">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:24">
-      <c r="B22" s="3">
+    <row r="22" ht="15" customHeight="1" spans="1:24">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
         <v>18</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="1">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="1">
         <v>5</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="G22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="1">
         <v>1918</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1">
         <v>5006</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>5002</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="P22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
         <v>700</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:24">
-      <c r="B23" s="3">
+    <row r="23" ht="15" customHeight="1" spans="1:24">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
         <v>19</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="1">
         <v>4</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="1">
         <v>4</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="G23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="1">
         <v>1919</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>1</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1">
         <v>6001</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="P23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q23" s="1">
         <v>2</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="1">
         <v>3</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="S23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U23" s="1">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="V23" s="1">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:24">
-      <c r="B24" s="3">
+    <row r="24" ht="15" customHeight="1" spans="1:24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
         <v>20</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="1">
         <v>4</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="G24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="1">
         <v>1920</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1">
         <v>6002</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="P24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q24" s="1">
         <v>2</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="1">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="S24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="U24" s="1">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="V24" s="1">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:24">
-      <c r="B25" s="3">
+    <row r="25" ht="15" customHeight="1" spans="1:24">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
         <v>21</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="1">
         <v>4</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="3">
+      <c r="G25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H25" s="1">
         <v>1921</v>
       </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>1</v>
-      </c>
-      <c r="L25" s="3">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3">
-        <v>1</v>
-      </c>
-      <c r="O25" s="3">
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1">
         <v>6003</v>
       </c>
-      <c r="P25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q25" s="3">
+      <c r="P25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q25" s="1">
         <v>2</v>
       </c>
-      <c r="R25" s="3">
+      <c r="R25" s="1">
         <v>3</v>
       </c>
-      <c r="S25" s="3">
-        <v>0</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="U25" s="3">
+      <c r="S25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="U25" s="1">
         <v>600</v>
       </c>
-      <c r="V25" s="3">
+      <c r="V25" s="1">
         <v>1200</v>
       </c>
-      <c r="W25" s="3">
-        <v>0</v>
-      </c>
-      <c r="X25" s="3">
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:24">
-      <c r="B26" s="3">
+    <row r="26" ht="15" customHeight="1" spans="1:24">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
         <v>22</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="1">
         <v>4</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="1">
         <v>3</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="G26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="1">
         <v>1922</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1">
         <v>6004</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="P26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q26" s="1">
         <v>2</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="1">
         <v>3</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="S26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U26" s="1">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="1">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="W26" s="1">
+        <v>0</v>
+      </c>
+      <c r="X26" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:24">
-      <c r="B27" s="3">
+    <row r="27" ht="15" customHeight="1" spans="1:24">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1">
         <v>23</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="1">
         <v>3</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="G27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27" s="1">
         <v>1923</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1">
         <v>6005</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="P27" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q27" s="1">
         <v>2</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="1">
         <v>3</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="S27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="U27" s="1">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="V27" s="1">
         <v>400</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="2:24">
-      <c r="B28" s="3">
+    <row r="28" ht="15" customHeight="1" spans="1:24">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1">
         <v>24</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="1">
         <v>4</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="1">
         <v>4</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="3">
+      <c r="G28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28" s="1">
         <v>1924</v>
       </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
-        <v>1</v>
-      </c>
-      <c r="O28" s="3">
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
         <v>6006</v>
       </c>
-      <c r="P28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q28" s="3">
+      <c r="P28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q28" s="1">
         <v>2</v>
       </c>
-      <c r="R28" s="3">
+      <c r="R28" s="1">
         <v>3</v>
       </c>
-      <c r="S28" s="3">
-        <v>0</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="U28" s="3">
+      <c r="S28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="U28" s="1">
         <v>600</v>
       </c>
-      <c r="V28" s="3">
+      <c r="V28" s="1">
         <v>600</v>
       </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
         <v>4</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:24">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1">
+        <v>999</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="1">
+        <v>5</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1101</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>999999999</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U29" s="1">
+        <v>0</v>
+      </c>
+      <c r="V29" s="1">
+        <v>0</v>
+      </c>
+      <c r="W29" s="1">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:24">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1">
+        <v>9999</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="1">
+        <v>5</v>
+      </c>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1102</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>999999999</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U30" s="1">
+        <v>0</v>
+      </c>
+      <c r="V30" s="1">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:24">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1">
+        <v>99999</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1103</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>999999999</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U31" s="1">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1">
+        <v>0</v>
+      </c>
+      <c r="W31" s="1">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="134">
   <si>
     <t>#</t>
   </si>
@@ -98,9 +98,6 @@
     <t>MaxDurability</t>
   </si>
   <si>
-    <t>Rarity</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
   </si>
   <si>
     <t>最大耐久度</t>
-  </si>
-  <si>
-    <t>稀有度</t>
   </si>
   <si>
     <t>钱包</t>
@@ -447,14 +441,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -910,148 +897,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1409,8 +1396,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:W31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1432,10 +1419,9 @@
     <col min="21" max="21" width="11" customWidth="1"/>
     <col min="22" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1463,9 +1449,8 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1533,164 +1518,155 @@
       <c r="W2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="2" t="s">
+      <c r="U3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>24</v>
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:24">
+    <row r="5" ht="15" customHeight="1" spans="1:23">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1699,7 +1675,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H5" s="1">
         <v>1901</v>
@@ -1726,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -1735,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U5" s="1">
         <v>50</v>
@@ -1749,18 +1725,15 @@
       <c r="W5" s="1">
         <v>0</v>
       </c>
-      <c r="X5" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:24">
+    <row r="6" ht="15" customHeight="1" spans="1:23">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1769,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H6" s="1">
         <v>1902</v>
@@ -1796,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -1805,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U6" s="1">
         <v>10</v>
@@ -1819,18 +1792,15 @@
       <c r="W6" s="1">
         <v>0</v>
       </c>
-      <c r="X6" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:24">
+    <row r="7" ht="15" customHeight="1" spans="1:23">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1839,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H7" s="1">
         <v>1903</v>
@@ -1866,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="1">
         <v>0</v>
@@ -1875,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U7" s="1">
         <v>10</v>
@@ -1889,18 +1859,15 @@
       <c r="W7" s="1">
         <v>0</v>
       </c>
-      <c r="X7" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:24">
+    <row r="8" ht="15" customHeight="1" spans="1:23">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1909,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H8" s="1">
         <v>1904</v>
@@ -1936,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -1945,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U8" s="1">
         <v>100</v>
@@ -1959,18 +1926,15 @@
       <c r="W8" s="1">
         <v>0</v>
       </c>
-      <c r="X8" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:24">
+    <row r="9" ht="15" customHeight="1" spans="1:23">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1979,7 +1943,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H9" s="1">
         <v>1905</v>
@@ -2006,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="1">
         <v>0</v>
@@ -2015,10 +1979,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
@@ -2029,18 +1993,15 @@
       <c r="W9" s="1">
         <v>0</v>
       </c>
-      <c r="X9" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:24">
+    <row r="10" ht="15" customHeight="1" spans="1:23">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2049,7 +2010,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H10" s="1">
         <v>1906</v>
@@ -2076,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
@@ -2085,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
@@ -2099,18 +2060,15 @@
       <c r="W10" s="1">
         <v>0</v>
       </c>
-      <c r="X10" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:24">
+    <row r="11" ht="15" customHeight="1" spans="1:23">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2119,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H11" s="1">
         <v>1907</v>
@@ -2146,7 +2104,7 @@
         <v>3001</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
@@ -2155,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
@@ -2169,18 +2127,15 @@
       <c r="W11" s="1">
         <v>0</v>
       </c>
-      <c r="X11" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:24">
+    <row r="12" ht="15" customHeight="1" spans="1:23">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -2189,7 +2144,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H12" s="1">
         <v>1908</v>
@@ -2216,7 +2171,7 @@
         <v>3002</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q12" s="1">
         <v>0</v>
@@ -2225,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
@@ -2239,18 +2194,15 @@
       <c r="W12" s="1">
         <v>0</v>
       </c>
-      <c r="X12" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:24">
+    <row r="13" ht="15" customHeight="1" spans="1:23">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -2259,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H13" s="1">
         <v>1909</v>
@@ -2286,7 +2238,7 @@
         <v>3003</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q13" s="1">
         <v>0</v>
@@ -2295,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
@@ -2309,18 +2261,15 @@
       <c r="W13" s="1">
         <v>0</v>
       </c>
-      <c r="X13" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:24">
+    <row r="14" ht="15" customHeight="1" spans="1:23">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -2329,7 +2278,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H14" s="1">
         <v>1910</v>
@@ -2356,7 +2305,7 @@
         <v>4001</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="1">
         <v>2</v>
@@ -2365,10 +2314,10 @@
         <v>3</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="U14" s="1">
         <v>500</v>
@@ -2379,18 +2328,15 @@
       <c r="W14" s="1">
         <v>0</v>
       </c>
-      <c r="X14" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:24">
+    <row r="15" ht="15" customHeight="1" spans="1:23">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -2399,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H15" s="1">
         <v>1911</v>
@@ -2426,7 +2372,7 @@
         <v>4002</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q15" s="1">
         <v>2</v>
@@ -2435,10 +2381,10 @@
         <v>3</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="U15" s="1">
         <v>500</v>
@@ -2449,18 +2395,15 @@
       <c r="W15" s="1">
         <v>0</v>
       </c>
-      <c r="X15" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:24">
+    <row r="16" ht="15" customHeight="1" spans="1:23">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2469,7 +2412,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H16" s="1">
         <v>1912</v>
@@ -2496,7 +2439,7 @@
         <v>4003</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q16" s="1">
         <v>1</v>
@@ -2505,10 +2448,10 @@
         <v>2</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="U16" s="1">
         <v>300</v>
@@ -2519,18 +2462,15 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:24">
+    <row r="17" ht="15" customHeight="1" spans="1:23">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -2539,7 +2479,7 @@
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H17" s="1">
         <v>1913</v>
@@ -2566,7 +2506,7 @@
         <v>5001</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="1">
         <v>0</v>
@@ -2575,10 +2515,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
@@ -2589,18 +2529,15 @@
       <c r="W17" s="1">
         <v>0</v>
       </c>
-      <c r="X17" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:24">
+    <row r="18" ht="15" customHeight="1" spans="1:23">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -2609,7 +2546,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H18" s="1">
         <v>1914</v>
@@ -2636,7 +2573,7 @@
         <v>5002</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="1">
         <v>0</v>
@@ -2645,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U18" s="1">
         <v>0</v>
@@ -2659,18 +2596,15 @@
       <c r="W18" s="1">
         <v>0</v>
       </c>
-      <c r="X18" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:24">
+    <row r="19" ht="15" customHeight="1" spans="1:23">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>15</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2679,7 +2613,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H19" s="1">
         <v>1915</v>
@@ -2706,7 +2640,7 @@
         <v>5003</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="1">
         <v>0</v>
@@ -2715,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="U19" s="1">
         <v>0</v>
@@ -2729,18 +2663,15 @@
       <c r="W19" s="1">
         <v>0</v>
       </c>
-      <c r="X19" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:24">
+    <row r="20" ht="15" customHeight="1" spans="1:23">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -2749,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H20" s="1">
         <v>1916</v>
@@ -2776,7 +2707,7 @@
         <v>5004</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -2785,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
@@ -2799,18 +2730,15 @@
       <c r="W20" s="1">
         <v>0</v>
       </c>
-      <c r="X20" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:24">
+    <row r="21" ht="15" customHeight="1" spans="1:23">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>17</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -2819,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H21" s="1">
         <v>1917</v>
@@ -2846,7 +2774,7 @@
         <v>5005</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q21" s="1">
         <v>0</v>
@@ -2855,10 +2783,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -2869,18 +2797,15 @@
       <c r="W21" s="1">
         <v>0</v>
       </c>
-      <c r="X21" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:24">
+    <row r="22" ht="15" customHeight="1" spans="1:23">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -2889,7 +2814,7 @@
         <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H22" s="1">
         <v>1918</v>
@@ -2916,7 +2841,7 @@
         <v>5006</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q22" s="1">
         <v>0</v>
@@ -2925,10 +2850,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
@@ -2939,18 +2864,15 @@
       <c r="W22" s="1">
         <v>0</v>
       </c>
-      <c r="X22" s="1">
-        <v>5</v>
-      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:24">
+    <row r="23" ht="15" customHeight="1" spans="1:23">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E23" s="1">
         <v>4</v>
@@ -2959,7 +2881,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H23" s="1">
         <v>1919</v>
@@ -2986,7 +2908,7 @@
         <v>6001</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Q23" s="1">
         <v>2</v>
@@ -2995,10 +2917,10 @@
         <v>3</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="U23" s="1">
         <v>600</v>
@@ -3009,18 +2931,15 @@
       <c r="W23" s="1">
         <v>0</v>
       </c>
-      <c r="X23" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:24">
+    <row r="24" ht="15" customHeight="1" spans="1:23">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -3029,7 +2948,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H24" s="1">
         <v>1920</v>
@@ -3056,7 +2975,7 @@
         <v>6002</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q24" s="1">
         <v>2</v>
@@ -3065,10 +2984,10 @@
         <v>3</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U24" s="1">
         <v>400</v>
@@ -3079,18 +2998,15 @@
       <c r="W24" s="1">
         <v>0</v>
       </c>
-      <c r="X24" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:24">
+    <row r="25" ht="15" customHeight="1" spans="1:23">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>21</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3099,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H25" s="1">
         <v>1921</v>
@@ -3126,7 +3042,7 @@
         <v>6003</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q25" s="1">
         <v>2</v>
@@ -3135,10 +3051,10 @@
         <v>3</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U25" s="1">
         <v>600</v>
@@ -3149,18 +3065,15 @@
       <c r="W25" s="1">
         <v>0</v>
       </c>
-      <c r="X25" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:24">
+    <row r="26" ht="15" customHeight="1" spans="1:23">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>22</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
@@ -3169,7 +3082,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H26" s="1">
         <v>1922</v>
@@ -3196,7 +3109,7 @@
         <v>6004</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q26" s="1">
         <v>2</v>
@@ -3205,10 +3118,10 @@
         <v>3</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="U26" s="1">
         <v>400</v>
@@ -3219,18 +3132,15 @@
       <c r="W26" s="1">
         <v>0</v>
       </c>
-      <c r="X26" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:24">
+    <row r="27" ht="15" customHeight="1" spans="1:23">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>23</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
@@ -3239,7 +3149,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H27" s="1">
         <v>1923</v>
@@ -3266,7 +3176,7 @@
         <v>6005</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q27" s="1">
         <v>2</v>
@@ -3275,10 +3185,10 @@
         <v>3</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U27" s="1">
         <v>400</v>
@@ -3289,18 +3199,15 @@
       <c r="W27" s="1">
         <v>0</v>
       </c>
-      <c r="X27" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:24">
+    <row r="28" ht="15" customHeight="1" spans="1:23">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>24</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -3309,7 +3216,7 @@
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H28" s="1">
         <v>1924</v>
@@ -3336,7 +3243,7 @@
         <v>6006</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q28" s="1">
         <v>2</v>
@@ -3345,10 +3252,10 @@
         <v>3</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="U28" s="1">
         <v>600</v>
@@ -3359,18 +3266,15 @@
       <c r="W28" s="1">
         <v>0</v>
       </c>
-      <c r="X28" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:24">
+    <row r="29" ht="15" customHeight="1" spans="1:23">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>999</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E29" s="1">
         <v>5</v>
@@ -3379,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H29" s="1">
         <v>1101</v>
@@ -3406,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q29" s="1">
         <v>0</v>
@@ -3415,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U29" s="1">
         <v>0</v>
@@ -3429,18 +3333,15 @@
       <c r="W29" s="1">
         <v>0</v>
       </c>
-      <c r="X29" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:24">
+    <row r="30" ht="15" customHeight="1" spans="1:23">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>9999</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
@@ -3449,7 +3350,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H30" s="1">
         <v>1102</v>
@@ -3476,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q30" s="1">
         <v>0</v>
@@ -3485,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U30" s="1">
         <v>0</v>
@@ -3499,18 +3400,15 @@
       <c r="W30" s="1">
         <v>0</v>
       </c>
-      <c r="X30" s="1">
-        <v>4</v>
-      </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:24">
+    <row r="31" ht="15" customHeight="1" spans="1:23">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>99999</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
@@ -3519,7 +3417,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H31" s="1">
         <v>1103</v>
@@ -3546,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q31" s="1">
         <v>0</v>
@@ -3555,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
@@ -3568,9 +3466,6 @@
       </c>
       <c r="W31" s="1">
         <v>0</v>
-      </c>
-      <c r="X31" s="1">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="135">
   <si>
     <t>#</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>SellPrice</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
   <si>
     <t>Weight</t>
@@ -1396,7 +1399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1417,11 +1420,11 @@
     <col min="19" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="50" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="15" customWidth="1"/>
+    <col min="22" max="23" width="10" customWidth="1"/>
+    <col min="24" max="24" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,8 +1452,9 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1518,155 +1522,162 @@
       <c r="W2" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="X2" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="V3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="V4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="X4" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:23">
+    <row r="5" ht="15" customHeight="1" spans="1:24">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1675,7 +1686,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" s="1">
         <v>1901</v>
@@ -1702,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -1711,29 +1722,32 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U5" s="1">
         <v>50</v>
       </c>
       <c r="V5" s="1">
+        <v>120</v>
+      </c>
+      <c r="W5" s="1">
         <v>50</v>
       </c>
-      <c r="W5" s="1">
+      <c r="X5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:23">
+    <row r="6" ht="15" customHeight="1" spans="1:24">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1742,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H6" s="1">
         <v>1902</v>
@@ -1769,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -1778,29 +1792,32 @@
         <v>0</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U6" s="1">
         <v>10</v>
       </c>
       <c r="V6" s="1">
+        <v>40</v>
+      </c>
+      <c r="W6" s="1">
         <v>100</v>
       </c>
-      <c r="W6" s="1">
+      <c r="X6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:23">
+    <row r="7" ht="15" customHeight="1" spans="1:24">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1809,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7" s="1">
         <v>1903</v>
@@ -1836,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="1">
         <v>0</v>
@@ -1845,29 +1862,32 @@
         <v>0</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U7" s="1">
         <v>10</v>
       </c>
       <c r="V7" s="1">
+        <v>40</v>
+      </c>
+      <c r="W7" s="1">
         <v>100</v>
       </c>
-      <c r="W7" s="1">
+      <c r="X7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:23">
+    <row r="8" ht="15" customHeight="1" spans="1:24">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1876,7 +1896,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H8" s="1">
         <v>1904</v>
@@ -1903,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -1912,29 +1932,32 @@
         <v>0</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U8" s="1">
         <v>100</v>
       </c>
       <c r="V8" s="1">
+        <v>300</v>
+      </c>
+      <c r="W8" s="1">
         <v>200</v>
       </c>
-      <c r="W8" s="1">
+      <c r="X8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:23">
+    <row r="9" ht="15" customHeight="1" spans="1:24">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1943,7 +1966,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1">
         <v>1905</v>
@@ -1970,38 +1993,41 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>800</v>
+      </c>
+      <c r="W9" s="1">
         <v>50</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
-      <c r="V9" s="1">
-        <v>50</v>
-      </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:23">
+    <row r="10" ht="15" customHeight="1" spans="1:24">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2010,7 +2036,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H10" s="1">
         <v>1906</v>
@@ -2037,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
@@ -2046,29 +2072,32 @@
         <v>0</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
       </c>
       <c r="V10" s="1">
+        <v>800</v>
+      </c>
+      <c r="W10" s="1">
         <v>30</v>
       </c>
-      <c r="W10" s="1">
+      <c r="X10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:23">
+    <row r="11" ht="15" customHeight="1" spans="1:24">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2077,7 +2106,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" s="1">
         <v>1907</v>
@@ -2104,7 +2133,7 @@
         <v>3001</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
@@ -2113,29 +2142,32 @@
         <v>0</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
       </c>
       <c r="V11" s="1">
+        <v>800</v>
+      </c>
+      <c r="W11" s="1">
         <v>500</v>
       </c>
-      <c r="W11" s="1">
+      <c r="X11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:23">
+    <row r="12" ht="15" customHeight="1" spans="1:24">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -2144,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H12" s="1">
         <v>1908</v>
@@ -2171,7 +2203,7 @@
         <v>3002</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q12" s="1">
         <v>0</v>
@@ -2180,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
@@ -2192,17 +2224,20 @@
         <v>800</v>
       </c>
       <c r="W12" s="1">
+        <v>800</v>
+      </c>
+      <c r="X12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:23">
+    <row r="13" ht="15" customHeight="1" spans="1:24">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -2211,7 +2246,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H13" s="1">
         <v>1909</v>
@@ -2238,7 +2273,7 @@
         <v>3003</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="1">
         <v>0</v>
@@ -2247,29 +2282,32 @@
         <v>0</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
       </c>
       <c r="V13" s="1">
+        <v>800</v>
+      </c>
+      <c r="W13" s="1">
         <v>600</v>
       </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:23">
+    <row r="14" ht="15" customHeight="1" spans="1:24">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -2278,7 +2316,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H14" s="1">
         <v>1910</v>
@@ -2305,7 +2343,7 @@
         <v>4001</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q14" s="1">
         <v>2</v>
@@ -2314,29 +2352,32 @@
         <v>3</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U14" s="1">
         <v>500</v>
       </c>
       <c r="V14" s="1">
+        <v>800</v>
+      </c>
+      <c r="W14" s="1">
         <v>700</v>
       </c>
-      <c r="W14" s="1">
+      <c r="X14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:23">
+    <row r="15" ht="15" customHeight="1" spans="1:24">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -2345,7 +2386,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="1">
         <v>1911</v>
@@ -2372,7 +2413,7 @@
         <v>4002</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="1">
         <v>2</v>
@@ -2381,29 +2422,32 @@
         <v>3</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U15" s="1">
         <v>500</v>
       </c>
       <c r="V15" s="1">
+        <v>800</v>
+      </c>
+      <c r="W15" s="1">
         <v>1200</v>
       </c>
-      <c r="W15" s="1">
+      <c r="X15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:23">
+    <row r="16" ht="15" customHeight="1" spans="1:24">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2412,7 +2456,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" s="1">
         <v>1912</v>
@@ -2439,7 +2483,7 @@
         <v>4003</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q16" s="1">
         <v>1</v>
@@ -2448,29 +2492,32 @@
         <v>2</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U16" s="1">
         <v>300</v>
       </c>
       <c r="V16" s="1">
+        <v>500</v>
+      </c>
+      <c r="W16" s="1">
         <v>100</v>
       </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:23">
+    <row r="17" ht="15" customHeight="1" spans="1:24">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -2479,7 +2526,7 @@
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" s="1">
         <v>1913</v>
@@ -2506,7 +2553,7 @@
         <v>5001</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="1">
         <v>0</v>
@@ -2515,29 +2562,32 @@
         <v>0</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
       </c>
       <c r="V17" s="1">
+        <v>800</v>
+      </c>
+      <c r="W17" s="1">
         <v>500</v>
       </c>
-      <c r="W17" s="1">
+      <c r="X17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:23">
+    <row r="18" ht="15" customHeight="1" spans="1:24">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -2546,7 +2596,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H18" s="1">
         <v>1914</v>
@@ -2573,7 +2623,7 @@
         <v>5002</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q18" s="1">
         <v>0</v>
@@ -2582,10 +2632,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U18" s="1">
         <v>0</v>
@@ -2594,17 +2644,20 @@
         <v>800</v>
       </c>
       <c r="W18" s="1">
+        <v>800</v>
+      </c>
+      <c r="X18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:23">
+    <row r="19" ht="15" customHeight="1" spans="1:24">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>15</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2613,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" s="1">
         <v>1915</v>
@@ -2640,7 +2693,7 @@
         <v>5003</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q19" s="1">
         <v>0</v>
@@ -2649,29 +2702,32 @@
         <v>0</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="U19" s="1">
         <v>0</v>
       </c>
       <c r="V19" s="1">
+        <v>800</v>
+      </c>
+      <c r="W19" s="1">
         <v>600</v>
       </c>
-      <c r="W19" s="1">
+      <c r="X19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:23">
+    <row r="20" ht="15" customHeight="1" spans="1:24">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -2680,7 +2736,7 @@
         <v>5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H20" s="1">
         <v>1916</v>
@@ -2707,7 +2763,7 @@
         <v>5004</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -2716,29 +2772,32 @@
         <v>0</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
       </c>
       <c r="V20" s="1">
+        <v>800</v>
+      </c>
+      <c r="W20" s="1">
         <v>500</v>
       </c>
-      <c r="W20" s="1">
+      <c r="X20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:23">
+    <row r="21" ht="15" customHeight="1" spans="1:24">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>17</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -2747,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
         <v>1917</v>
@@ -2774,7 +2833,7 @@
         <v>5005</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q21" s="1">
         <v>0</v>
@@ -2783,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -2795,17 +2854,20 @@
         <v>800</v>
       </c>
       <c r="W21" s="1">
+        <v>800</v>
+      </c>
+      <c r="X21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:23">
+    <row r="22" ht="15" customHeight="1" spans="1:24">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -2814,7 +2876,7 @@
         <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H22" s="1">
         <v>1918</v>
@@ -2841,7 +2903,7 @@
         <v>5006</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q22" s="1">
         <v>0</v>
@@ -2850,29 +2912,32 @@
         <v>0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
       </c>
       <c r="V22" s="1">
+        <v>800</v>
+      </c>
+      <c r="W22" s="1">
         <v>700</v>
       </c>
-      <c r="W22" s="1">
+      <c r="X22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:23">
+    <row r="23" ht="15" customHeight="1" spans="1:24">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" s="1">
         <v>4</v>
@@ -2881,7 +2946,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H23" s="1">
         <v>1919</v>
@@ -2908,7 +2973,7 @@
         <v>6001</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q23" s="1">
         <v>2</v>
@@ -2917,29 +2982,32 @@
         <v>3</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U23" s="1">
         <v>600</v>
       </c>
       <c r="V23" s="1">
+        <v>1000</v>
+      </c>
+      <c r="W23" s="1">
         <v>700</v>
       </c>
-      <c r="W23" s="1">
+      <c r="X23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:23">
+    <row r="24" ht="15" customHeight="1" spans="1:24">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -2948,7 +3016,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H24" s="1">
         <v>1920</v>
@@ -2975,7 +3043,7 @@
         <v>6002</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q24" s="1">
         <v>2</v>
@@ -2984,29 +3052,32 @@
         <v>3</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U24" s="1">
         <v>400</v>
       </c>
       <c r="V24" s="1">
+        <v>700</v>
+      </c>
+      <c r="W24" s="1">
         <v>500</v>
       </c>
-      <c r="W24" s="1">
+      <c r="X24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:23">
+    <row r="25" ht="15" customHeight="1" spans="1:24">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>21</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3015,7 +3086,7 @@
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H25" s="1">
         <v>1921</v>
@@ -3042,7 +3113,7 @@
         <v>6003</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q25" s="1">
         <v>2</v>
@@ -3051,29 +3122,32 @@
         <v>3</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U25" s="1">
         <v>600</v>
       </c>
       <c r="V25" s="1">
+        <v>1000</v>
+      </c>
+      <c r="W25" s="1">
         <v>1200</v>
       </c>
-      <c r="W25" s="1">
+      <c r="X25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:23">
+    <row r="26" ht="15" customHeight="1" spans="1:24">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>22</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
@@ -3082,7 +3156,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H26" s="1">
         <v>1922</v>
@@ -3109,7 +3183,7 @@
         <v>6004</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q26" s="1">
         <v>2</v>
@@ -3118,29 +3192,32 @@
         <v>3</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="U26" s="1">
         <v>400</v>
       </c>
       <c r="V26" s="1">
+        <v>700</v>
+      </c>
+      <c r="W26" s="1">
         <v>300</v>
       </c>
-      <c r="W26" s="1">
+      <c r="X26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:23">
+    <row r="27" ht="15" customHeight="1" spans="1:24">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>23</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
@@ -3149,7 +3226,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H27" s="1">
         <v>1923</v>
@@ -3176,7 +3253,7 @@
         <v>6005</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q27" s="1">
         <v>2</v>
@@ -3185,29 +3262,32 @@
         <v>3</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U27" s="1">
         <v>400</v>
       </c>
       <c r="V27" s="1">
+        <v>700</v>
+      </c>
+      <c r="W27" s="1">
         <v>400</v>
       </c>
-      <c r="W27" s="1">
+      <c r="X27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:23">
+    <row r="28" ht="15" customHeight="1" spans="1:24">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>24</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -3216,7 +3296,7 @@
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H28" s="1">
         <v>1924</v>
@@ -3243,7 +3323,7 @@
         <v>6006</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q28" s="1">
         <v>2</v>
@@ -3252,29 +3332,32 @@
         <v>3</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U28" s="1">
         <v>600</v>
       </c>
       <c r="V28" s="1">
+        <v>1000</v>
+      </c>
+      <c r="W28" s="1">
         <v>600</v>
       </c>
-      <c r="W28" s="1">
+      <c r="X28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:23">
+    <row r="29" ht="15" customHeight="1" spans="1:24">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>999</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" s="1">
         <v>5</v>
@@ -3283,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H29" s="1">
         <v>1101</v>
@@ -3310,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q29" s="1">
         <v>0</v>
@@ -3319,29 +3402,32 @@
         <v>0</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U29" s="1">
         <v>0</v>
       </c>
       <c r="V29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="1">
         <v>0</v>
       </c>
+      <c r="X29" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:23">
+    <row r="30" ht="15" customHeight="1" spans="1:24">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>9999</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
@@ -3350,7 +3436,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H30" s="1">
         <v>1102</v>
@@ -3377,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q30" s="1">
         <v>0</v>
@@ -3386,29 +3472,32 @@
         <v>0</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U30" s="1">
         <v>0</v>
       </c>
       <c r="V30" s="1">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="W30" s="1">
         <v>0</v>
       </c>
+      <c r="X30" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:23">
+    <row r="31" ht="15" customHeight="1" spans="1:24">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>99999</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
@@ -3417,7 +3506,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H31" s="1">
         <v>1103</v>
@@ -3444,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q31" s="1">
         <v>0</v>
@@ -3453,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
@@ -3465,6 +3554,9 @@
         <v>0</v>
       </c>
       <c r="W31" s="1">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="183">
   <si>
     <t>#</t>
   </si>
@@ -414,6 +414,150 @@
   </si>
   <si>
     <t>{"MagicPower":"200","CooldownReduction":"15%","AttackSpeed":"10%"}</t>
+  </si>
+  <si>
+    <t>卡牌-神圣庇护</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：神圣庇护</t>
+  </si>
+  <si>
+    <t>卡牌-烈焰风暴</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：烈焰风暴</t>
+  </si>
+  <si>
+    <t>卡牌-时间回溯</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：时间回溯</t>
+  </si>
+  <si>
+    <t>卡牌-战争号角</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：战争号角</t>
+  </si>
+  <si>
+    <t>卡牌-暗影突袭</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：暗影突袭</t>
+  </si>
+  <si>
+    <t>卡牌-生命汲取</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：生命汲取</t>
+  </si>
+  <si>
+    <t>卡牌-冰霜新星</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：冰霜新星</t>
+  </si>
+  <si>
+    <t>卡牌-狂暴</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：狂暴</t>
+  </si>
+  <si>
+    <t>卡牌-群体治疗</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：群体治疗</t>
+  </si>
+  <si>
+    <t>卡牌-雷霆一击</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：雷霆一击</t>
+  </si>
+  <si>
+    <t>卡牌-混乱诅咒</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：混乱诅咒</t>
+  </si>
+  <si>
+    <t>卡牌-不屈意志</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：不屈意志</t>
+  </si>
+  <si>
+    <t>卡牌-反伤之盾</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：反伤之盾</t>
+  </si>
+  <si>
+    <t>卡牌-圣域防线</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：圣域防线</t>
+  </si>
+  <si>
+    <t>卡牌-护盾再生</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：护盾再生</t>
+  </si>
+  <si>
+    <t>卡牌-救赎之光</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：救赎之光</t>
+  </si>
+  <si>
+    <t>卡牌-血源强化</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：血源强化</t>
+  </si>
+  <si>
+    <t>卡牌-吸血之刃</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：吸血之刃</t>
+  </si>
+  <si>
+    <t>卡牌-灾厄之雷</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：灾厄之雷</t>
+  </si>
+  <si>
+    <t>卡牌-护甲破碎</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：护甲破碎</t>
+  </si>
+  <si>
+    <t>卡牌-虚弱诅咒</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：虚弱诅咒</t>
+  </si>
+  <si>
+    <t>卡牌-沉默之符</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：沉默之符</t>
+  </si>
+  <si>
+    <t>卡牌-嘲讽之声</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：嘲讽之声</t>
+  </si>
+  <si>
+    <t>卡牌-剧毒之雾</t>
+  </si>
+  <si>
+    <t>使用后解锁卡牌：剧毒之雾</t>
   </si>
   <si>
     <t>金币</t>
@@ -444,7 +588,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,31 +1051,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -933,115 +1081,118 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1399,13 +1550,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
@@ -1420,7 +1571,8 @@
     <col min="19" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="50" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="23" width="10" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3353,23 +3505,23 @@
     <row r="29" ht="15" customHeight="1" spans="1:24">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
         <v>129</v>
       </c>
       <c r="E29" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H29" s="1">
-        <v>1101</v>
+        <v>1925</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3378,13 +3530,13 @@
         <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>999999999</v>
+        <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="1">
-        <v>0</v>
+        <v>2001</v>
       </c>
       <c r="N29" s="1">
         <v>0</v>
@@ -3408,13 +3560,13 @@
         <v>52</v>
       </c>
       <c r="U29" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V29" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="W29" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X29" s="1">
         <v>0</v>
@@ -3423,23 +3575,23 @@
     <row r="30" ht="15" customHeight="1" spans="1:24">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>9999</v>
+        <v>101</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
         <v>131</v>
       </c>
       <c r="E30" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>132</v>
       </c>
       <c r="H30" s="1">
-        <v>1102</v>
+        <v>1926</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3448,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>999999999</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="1">
-        <v>0</v>
+        <v>2002</v>
       </c>
       <c r="N30" s="1">
         <v>0</v>
@@ -3478,13 +3630,13 @@
         <v>52</v>
       </c>
       <c r="U30" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V30" s="1">
-        <v>999</v>
+        <v>300</v>
       </c>
       <c r="W30" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -3493,14 +3645,14 @@
     <row r="31" ht="15" customHeight="1" spans="1:24">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>99999</v>
+        <v>102</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
         <v>133</v>
       </c>
       <c r="E31" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
@@ -3509,7 +3661,7 @@
         <v>134</v>
       </c>
       <c r="H31" s="1">
-        <v>1103</v>
+        <v>1927</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -3518,13 +3670,13 @@
         <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>999999999</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="1">
-        <v>0</v>
+        <v>2003</v>
       </c>
       <c r="N31" s="1">
         <v>0</v>
@@ -3548,15 +3700,1695 @@
         <v>52</v>
       </c>
       <c r="U31" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V31" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W31" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:24">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1">
+        <v>103</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1928</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
+        <v>2004</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U32" s="1">
+        <v>30</v>
+      </c>
+      <c r="V32" s="1">
+        <v>100</v>
+      </c>
+      <c r="W32" s="1">
+        <v>50</v>
+      </c>
+      <c r="X32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:24">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1">
+        <v>104</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>3</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1929</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
+        <v>2005</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" s="1">
+        <v>50</v>
+      </c>
+      <c r="V33" s="1">
+        <v>300</v>
+      </c>
+      <c r="W33" s="1">
+        <v>50</v>
+      </c>
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:24">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1">
+        <v>105</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1930</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1">
+        <v>2006</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U34" s="1">
+        <v>50</v>
+      </c>
+      <c r="V34" s="1">
+        <v>300</v>
+      </c>
+      <c r="W34" s="1">
+        <v>50</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:24">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1">
+        <v>106</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1931</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1">
+        <v>2007</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U35" s="1">
+        <v>30</v>
+      </c>
+      <c r="V35" s="1">
+        <v>100</v>
+      </c>
+      <c r="W35" s="1">
+        <v>50</v>
+      </c>
+      <c r="X35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:24">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1">
+        <v>107</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1932</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
+        <v>2008</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U36" s="1">
+        <v>30</v>
+      </c>
+      <c r="V36" s="1">
+        <v>100</v>
+      </c>
+      <c r="W36" s="1">
+        <v>50</v>
+      </c>
+      <c r="X36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:24">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1">
+        <v>108</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1933</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
+        <v>2009</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U37" s="1">
+        <v>30</v>
+      </c>
+      <c r="V37" s="1">
+        <v>100</v>
+      </c>
+      <c r="W37" s="1">
+        <v>50</v>
+      </c>
+      <c r="X37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:24">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1">
+        <v>109</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1934</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
+        <v>2010</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U38" s="1">
+        <v>100</v>
+      </c>
+      <c r="V38" s="1">
+        <v>800</v>
+      </c>
+      <c r="W38" s="1">
+        <v>50</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:24">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1">
+        <v>110</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1935</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2011</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U39" s="1">
+        <v>50</v>
+      </c>
+      <c r="V39" s="1">
+        <v>300</v>
+      </c>
+      <c r="W39" s="1">
+        <v>50</v>
+      </c>
+      <c r="X39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:24">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1">
+        <v>111</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1936</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2012</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U40" s="1">
+        <v>100</v>
+      </c>
+      <c r="V40" s="1">
+        <v>800</v>
+      </c>
+      <c r="W40" s="1">
+        <v>50</v>
+      </c>
+      <c r="X40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:24">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1">
+        <v>112</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1937</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2013</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U41" s="1">
+        <v>30</v>
+      </c>
+      <c r="V41" s="1">
+        <v>100</v>
+      </c>
+      <c r="W41" s="1">
+        <v>50</v>
+      </c>
+      <c r="X41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:24">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1">
+        <v>113</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1938</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2014</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U42" s="1">
+        <v>50</v>
+      </c>
+      <c r="V42" s="1">
+        <v>300</v>
+      </c>
+      <c r="W42" s="1">
+        <v>50</v>
+      </c>
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:24">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1">
+        <v>114</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1939</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2015</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U43" s="1">
+        <v>50</v>
+      </c>
+      <c r="V43" s="1">
+        <v>300</v>
+      </c>
+      <c r="W43" s="1">
+        <v>50</v>
+      </c>
+      <c r="X43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:24">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1">
+        <v>115</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1940</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2016</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U44" s="1">
+        <v>50</v>
+      </c>
+      <c r="V44" s="1">
+        <v>300</v>
+      </c>
+      <c r="W44" s="1">
+        <v>50</v>
+      </c>
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:24">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1">
+        <v>116</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1941</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1">
+        <v>2017</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U45" s="1">
+        <v>50</v>
+      </c>
+      <c r="V45" s="1">
+        <v>300</v>
+      </c>
+      <c r="W45" s="1">
+        <v>50</v>
+      </c>
+      <c r="X45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:24">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1">
+        <v>117</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1942</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2018</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U46" s="1">
+        <v>50</v>
+      </c>
+      <c r="V46" s="1">
+        <v>300</v>
+      </c>
+      <c r="W46" s="1">
+        <v>50</v>
+      </c>
+      <c r="X46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:24">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1">
+        <v>118</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>3</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1943</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>1</v>
+      </c>
+      <c r="M47" s="1">
+        <v>2019</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U47" s="1">
+        <v>50</v>
+      </c>
+      <c r="V47" s="1">
+        <v>300</v>
+      </c>
+      <c r="W47" s="1">
+        <v>50</v>
+      </c>
+      <c r="X47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="1:24">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1">
+        <v>119</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>3</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1944</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <v>2020</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U48" s="1">
+        <v>50</v>
+      </c>
+      <c r="V48" s="1">
+        <v>300</v>
+      </c>
+      <c r="W48" s="1">
+        <v>50</v>
+      </c>
+      <c r="X48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:24">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1">
+        <v>120</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>2</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1945</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <v>2021</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U49" s="1">
+        <v>30</v>
+      </c>
+      <c r="V49" s="1">
+        <v>100</v>
+      </c>
+      <c r="W49" s="1">
+        <v>50</v>
+      </c>
+      <c r="X49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" spans="1:24">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1">
+        <v>121</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
+        <v>3</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1946</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2022</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U50" s="1">
+        <v>50</v>
+      </c>
+      <c r="V50" s="1">
+        <v>300</v>
+      </c>
+      <c r="W50" s="1">
+        <v>50</v>
+      </c>
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" spans="1:24">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1">
+        <v>122</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
+        <v>2</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H51" s="1">
+        <v>1947</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
+        <v>2023</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U51" s="1">
+        <v>30</v>
+      </c>
+      <c r="V51" s="1">
+        <v>100</v>
+      </c>
+      <c r="W51" s="1">
+        <v>50</v>
+      </c>
+      <c r="X51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" spans="1:24">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1">
+        <v>123</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1948</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
+        <v>2024</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U52" s="1">
+        <v>30</v>
+      </c>
+      <c r="V52" s="1">
+        <v>100</v>
+      </c>
+      <c r="W52" s="1">
+        <v>50</v>
+      </c>
+      <c r="X52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:24">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1">
+        <v>999</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" s="1">
+        <v>5</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1101</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>999999999</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U53" s="1">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
+        <v>1</v>
+      </c>
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="1:24">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1">
+        <v>9999</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" s="1">
+        <v>5</v>
+      </c>
+      <c r="F54" s="1">
+        <v>4</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1102</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>999999999</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="O54" s="1">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <v>999</v>
+      </c>
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:24">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1">
+        <v>99999</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" s="1">
+        <v>5</v>
+      </c>
+      <c r="F55" s="1">
+        <v>3</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1103</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>999999999</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U55" s="1">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1">
+        <v>0</v>
+      </c>
+      <c r="X55" s="1">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="186">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Quality</t>
   </si>
   <si>
+    <t>IsOnlyInGame</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>int[]</t>
   </si>
   <si>
@@ -123,6 +129,9 @@
   </si>
   <si>
     <t>品质等级</t>
+  </si>
+  <si>
+    <t>是否只在局内使用</t>
   </si>
   <si>
     <t>物品描述</t>
@@ -588,14 +597,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1051,28 +1053,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1081,118 +1086,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1550,7 +1552,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1558,25 +1560,26 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="50" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="8" customWidth="1"/>
-    <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
+    <col min="21" max="21" width="50" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="8" customWidth="1"/>
+    <col min="24" max="24" width="10" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1596,17 +1599,18 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="2"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1650,19 +1654,19 @@
       <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="U2" s="1" t="s">
@@ -1677,159 +1681,168 @@
       <c r="X2" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y2" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="P4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="R4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="S4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="U4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="1"/>
       <c r="X4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:24">
+    <row r="5" ht="15" customHeight="1" spans="1:25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1837,69 +1850,72 @@
       <c r="F5" s="1">
         <v>2</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1901</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>99</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V5" s="1">
         <v>50</v>
       </c>
-      <c r="H5" s="1">
-        <v>1901</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>99</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U5" s="1">
+      <c r="W5" s="1">
+        <v>120</v>
+      </c>
+      <c r="X5" s="1">
         <v>50</v>
       </c>
-      <c r="V5" s="1">
-        <v>120</v>
-      </c>
-      <c r="W5" s="1">
-        <v>50</v>
-      </c>
-      <c r="X5" s="1">
+      <c r="Y5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:24">
+    <row r="6" ht="15" customHeight="1" spans="1:25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1907,139 +1923,145 @@
       <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="1">
         <v>1902</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
         <v>99</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
       <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
         <v>1002</v>
       </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U6" s="1">
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" s="1">
         <v>10</v>
       </c>
-      <c r="V6" s="1">
+      <c r="W6" s="1">
         <v>40</v>
       </c>
-      <c r="W6" s="1">
+      <c r="X6" s="1">
         <v>100</v>
       </c>
-      <c r="X6" s="1">
+      <c r="Y6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:24">
+    <row r="7" ht="15" customHeight="1" spans="1:25">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1903</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>99</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1003</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1903</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>99</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1003</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U7" s="1">
+      <c r="V7" s="1">
         <v>10</v>
       </c>
-      <c r="V7" s="1">
+      <c r="W7" s="1">
         <v>40</v>
       </c>
-      <c r="W7" s="1">
+      <c r="X7" s="1">
         <v>100</v>
       </c>
-      <c r="X7" s="1">
+      <c r="Y7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:24">
+    <row r="8" ht="15" customHeight="1" spans="1:25">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2047,69 +2069,72 @@
       <c r="F8" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="G8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="1">
         <v>1904</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
       <c r="J8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
         <v>20</v>
       </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
       <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
         <v>1004</v>
       </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U8" s="1">
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V8" s="1">
         <v>100</v>
       </c>
-      <c r="V8" s="1">
+      <c r="W8" s="1">
         <v>300</v>
       </c>
-      <c r="W8" s="1">
+      <c r="X8" s="1">
         <v>200</v>
       </c>
-      <c r="X8" s="1">
+      <c r="Y8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:24">
+    <row r="9" ht="15" customHeight="1" spans="1:25">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -2117,23 +2142,23 @@
       <c r="F9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="G9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="1">
         <v>1905</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -2144,42 +2169,45 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
       </c>
-      <c r="S9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
         <v>800</v>
       </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
         <v>50</v>
       </c>
-      <c r="X9" s="1">
+      <c r="Y9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:24">
+    <row r="10" ht="15" customHeight="1" spans="1:25">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2187,23 +2215,23 @@
       <c r="F10" s="1">
         <v>4</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="G10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="1">
         <v>1906</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
       <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
@@ -2214,42 +2242,45 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
         <v>800</v>
       </c>
-      <c r="W10" s="1">
+      <c r="X10" s="1">
         <v>30</v>
       </c>
-      <c r="X10" s="1">
+      <c r="Y10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:24">
+    <row r="11" ht="15" customHeight="1" spans="1:25">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2257,69 +2288,72 @@
       <c r="F11" s="1">
         <v>5</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="1">
         <v>1907</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
         <v>3001</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
+      <c r="Q11" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R11" s="1">
         <v>0</v>
       </c>
-      <c r="S11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1">
         <v>800</v>
       </c>
-      <c r="W11" s="1">
+      <c r="X11" s="1">
         <v>500</v>
       </c>
-      <c r="X11" s="1">
+      <c r="Y11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:24">
+    <row r="12" ht="15" customHeight="1" spans="1:25">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -2327,69 +2361,72 @@
       <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1908</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>3002</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H12" s="1">
-        <v>1908</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>3002</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
+      <c r="U12" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="V12" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="W12" s="1">
         <v>800</v>
       </c>
       <c r="X12" s="1">
+        <v>800</v>
+      </c>
+      <c r="Y12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:24">
+    <row r="13" ht="15" customHeight="1" spans="1:25">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -2397,69 +2434,72 @@
       <c r="F13" s="1">
         <v>5</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="G13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="1">
         <v>1909</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
       <c r="J13" s="1">
         <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
         <v>3003</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
+      <c r="Q13" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
-      <c r="S13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U13" s="1">
-        <v>0</v>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
         <v>800</v>
       </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
         <v>600</v>
       </c>
-      <c r="X13" s="1">
+      <c r="Y13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:24">
+    <row r="14" ht="15" customHeight="1" spans="1:25">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -2467,69 +2507,72 @@
       <c r="F14" s="1">
         <v>4</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="G14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="1">
         <v>1910</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
       <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
         <v>4001</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="R14" s="1">
         <v>2</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <v>3</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="U14" s="1">
+      <c r="T14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="V14" s="1">
         <v>500</v>
       </c>
-      <c r="V14" s="1">
+      <c r="W14" s="1">
         <v>800</v>
       </c>
-      <c r="W14" s="1">
+      <c r="X14" s="1">
         <v>700</v>
       </c>
-      <c r="X14" s="1">
+      <c r="Y14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:24">
+    <row r="15" ht="15" customHeight="1" spans="1:25">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -2537,69 +2580,72 @@
       <c r="F15" s="1">
         <v>4</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="G15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="1">
         <v>1911</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
         <v>4002</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R15" s="1">
         <v>2</v>
       </c>
-      <c r="R15" s="1">
+      <c r="S15" s="1">
         <v>3</v>
       </c>
-      <c r="S15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="U15" s="1">
+      <c r="T15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="V15" s="1">
         <v>500</v>
       </c>
-      <c r="V15" s="1">
+      <c r="W15" s="1">
         <v>800</v>
       </c>
-      <c r="W15" s="1">
+      <c r="X15" s="1">
         <v>1200</v>
       </c>
-      <c r="X15" s="1">
+      <c r="Y15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:24">
+    <row r="16" ht="15" customHeight="1" spans="1:25">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2607,69 +2653,72 @@
       <c r="F16" s="1">
         <v>3</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="G16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="1">
         <v>1912</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
         <v>4003</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>1</v>
+      <c r="Q16" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="R16" s="1">
+        <v>1</v>
+      </c>
+      <c r="S16" s="1">
         <v>2</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="U16" s="1">
+      <c r="T16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V16" s="1">
         <v>300</v>
       </c>
-      <c r="V16" s="1">
+      <c r="W16" s="1">
         <v>500</v>
       </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
         <v>100</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:24">
+    <row r="17" ht="15" customHeight="1" spans="1:25">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -2677,69 +2726,72 @@
       <c r="F17" s="1">
         <v>5</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="G17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="1">
         <v>1913</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
         <v>5001</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
+      <c r="Q17" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R17" s="1">
         <v>0</v>
       </c>
-      <c r="S17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="U17" s="1">
-        <v>0</v>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
         <v>800</v>
       </c>
-      <c r="W17" s="1">
+      <c r="X17" s="1">
         <v>500</v>
       </c>
-      <c r="X17" s="1">
+      <c r="Y17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:24">
+    <row r="18" ht="15" customHeight="1" spans="1:25">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -2747,69 +2799,72 @@
       <c r="F18" s="1">
         <v>5</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1914</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>5002</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H18" s="1">
-        <v>1914</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
-      <c r="O18" s="1">
-        <v>5002</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="U18" s="1">
-        <v>0</v>
+      <c r="U18" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="V18" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="W18" s="1">
         <v>800</v>
       </c>
       <c r="X18" s="1">
+        <v>800</v>
+      </c>
+      <c r="Y18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:24">
+    <row r="19" ht="15" customHeight="1" spans="1:25">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>15</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2817,69 +2872,72 @@
       <c r="F19" s="1">
         <v>5</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="G19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="1">
         <v>1915</v>
       </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
       <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1">
         <v>5003</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
+      <c r="Q19" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R19" s="1">
         <v>0</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
         <v>800</v>
       </c>
-      <c r="W19" s="1">
+      <c r="X19" s="1">
         <v>600</v>
       </c>
-      <c r="X19" s="1">
+      <c r="Y19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:24">
+    <row r="20" ht="15" customHeight="1" spans="1:25">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -2887,69 +2945,72 @@
       <c r="F20" s="1">
         <v>5</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="G20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" s="1">
         <v>1916</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
+        <v>1</v>
+      </c>
+      <c r="P20" s="1">
         <v>5004</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
+      <c r="Q20" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="U20" s="1">
-        <v>0</v>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
         <v>800</v>
       </c>
-      <c r="W20" s="1">
+      <c r="X20" s="1">
         <v>500</v>
       </c>
-      <c r="X20" s="1">
+      <c r="Y20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:24">
+    <row r="21" ht="15" customHeight="1" spans="1:25">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>17</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -2957,69 +3018,72 @@
       <c r="F21" s="1">
         <v>5</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1917</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1">
+        <v>5005</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="1">
-        <v>1917</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>1</v>
-      </c>
-      <c r="O21" s="1">
-        <v>5005</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
+      <c r="U21" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="V21" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="W21" s="1">
         <v>800</v>
       </c>
       <c r="X21" s="1">
+        <v>800</v>
+      </c>
+      <c r="Y21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:24">
+    <row r="22" ht="15" customHeight="1" spans="1:25">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -3027,69 +3091,72 @@
       <c r="F22" s="1">
         <v>5</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="G22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="1">
         <v>1918</v>
       </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
       <c r="J22" s="1">
         <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="1">
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1">
         <v>5006</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
+      <c r="Q22" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
       </c>
-      <c r="S22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
         <v>800</v>
       </c>
-      <c r="W22" s="1">
+      <c r="X22" s="1">
         <v>700</v>
       </c>
-      <c r="X22" s="1">
+      <c r="Y22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:24">
+    <row r="23" ht="15" customHeight="1" spans="1:25">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E23" s="1">
         <v>4</v>
@@ -3097,69 +3164,72 @@
       <c r="F23" s="1">
         <v>4</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="G23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="1">
         <v>1919</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
       <c r="J23" s="1">
         <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="1">
         <v>6001</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="R23" s="1">
         <v>2</v>
       </c>
-      <c r="R23" s="1">
+      <c r="S23" s="1">
         <v>3</v>
       </c>
-      <c r="S23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="U23" s="1">
+      <c r="T23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="V23" s="1">
         <v>600</v>
       </c>
-      <c r="V23" s="1">
+      <c r="W23" s="1">
         <v>1000</v>
       </c>
-      <c r="W23" s="1">
+      <c r="X23" s="1">
         <v>700</v>
       </c>
-      <c r="X23" s="1">
+      <c r="Y23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:24">
+    <row r="24" ht="15" customHeight="1" spans="1:25">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -3167,69 +3237,72 @@
       <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="G24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="1">
         <v>1920</v>
       </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
       <c r="J24" s="1">
         <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1">
         <v>6002</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="1">
         <v>2</v>
       </c>
-      <c r="R24" s="1">
+      <c r="S24" s="1">
         <v>3</v>
       </c>
-      <c r="S24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="U24" s="1">
+      <c r="T24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="V24" s="1">
         <v>400</v>
       </c>
-      <c r="V24" s="1">
+      <c r="W24" s="1">
         <v>700</v>
       </c>
-      <c r="W24" s="1">
+      <c r="X24" s="1">
         <v>500</v>
       </c>
-      <c r="X24" s="1">
+      <c r="Y24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:24">
+    <row r="25" ht="15" customHeight="1" spans="1:25">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>21</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3237,69 +3310,72 @@
       <c r="F25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="G25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="1">
         <v>1921</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
       <c r="J25" s="1">
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1">
+        <v>1</v>
+      </c>
+      <c r="P25" s="1">
         <v>6003</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="R25" s="1">
         <v>2</v>
       </c>
-      <c r="R25" s="1">
+      <c r="S25" s="1">
         <v>3</v>
       </c>
-      <c r="S25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U25" s="1">
+      <c r="T25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="V25" s="1">
         <v>600</v>
       </c>
-      <c r="V25" s="1">
+      <c r="W25" s="1">
         <v>1000</v>
       </c>
-      <c r="W25" s="1">
+      <c r="X25" s="1">
         <v>1200</v>
       </c>
-      <c r="X25" s="1">
+      <c r="Y25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:24">
+    <row r="26" ht="15" customHeight="1" spans="1:25">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>22</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
@@ -3307,69 +3383,72 @@
       <c r="F26" s="1">
         <v>3</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="G26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="1">
         <v>1922</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
       <c r="J26" s="1">
         <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
+        <v>1</v>
+      </c>
+      <c r="P26" s="1">
         <v>6004</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R26" s="1">
         <v>2</v>
       </c>
-      <c r="R26" s="1">
+      <c r="S26" s="1">
         <v>3</v>
       </c>
-      <c r="S26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="U26" s="1">
+      <c r="T26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="V26" s="1">
         <v>400</v>
       </c>
-      <c r="V26" s="1">
+      <c r="W26" s="1">
         <v>700</v>
       </c>
-      <c r="W26" s="1">
+      <c r="X26" s="1">
         <v>300</v>
       </c>
-      <c r="X26" s="1">
+      <c r="Y26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:24">
+    <row r="27" ht="15" customHeight="1" spans="1:25">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>23</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
@@ -3377,69 +3456,72 @@
       <c r="F27" s="1">
         <v>3</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="G27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="1">
         <v>1923</v>
       </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
       <c r="J27" s="1">
         <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
+        <v>1</v>
+      </c>
+      <c r="P27" s="1">
         <v>6005</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="R27" s="1">
         <v>2</v>
       </c>
-      <c r="R27" s="1">
+      <c r="S27" s="1">
         <v>3</v>
       </c>
-      <c r="S27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="U27" s="1">
+      <c r="T27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="V27" s="1">
         <v>400</v>
       </c>
-      <c r="V27" s="1">
+      <c r="W27" s="1">
         <v>700</v>
       </c>
-      <c r="W27" s="1">
+      <c r="X27" s="1">
         <v>400</v>
       </c>
-      <c r="X27" s="1">
+      <c r="Y27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:24">
+    <row r="28" ht="15" customHeight="1" spans="1:25">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>24</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -3447,69 +3529,72 @@
       <c r="F28" s="1">
         <v>4</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="G28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="1">
         <v>1924</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
       <c r="J28" s="1">
         <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
+        <v>1</v>
+      </c>
+      <c r="P28" s="1">
         <v>6006</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="R28" s="1">
         <v>2</v>
       </c>
-      <c r="R28" s="1">
+      <c r="S28" s="1">
         <v>3</v>
       </c>
-      <c r="S28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="U28" s="1">
+      <c r="T28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="V28" s="1">
         <v>600</v>
       </c>
-      <c r="V28" s="1">
+      <c r="W28" s="1">
         <v>1000</v>
       </c>
-      <c r="W28" s="1">
+      <c r="X28" s="1">
         <v>600</v>
       </c>
-      <c r="X28" s="1">
+      <c r="Y28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:24">
+    <row r="29" ht="15" customHeight="1" spans="1:25">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>100</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3517,17 +3602,17 @@
       <c r="F29" s="1">
         <v>2</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="G29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="1">
         <v>1925</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
       <c r="J29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
@@ -3536,50 +3621,53 @@
         <v>1</v>
       </c>
       <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1">
         <v>2001</v>
       </c>
-      <c r="N29" s="1">
-        <v>0</v>
-      </c>
       <c r="O29" s="1">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>0</v>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R29" s="1">
         <v>0</v>
       </c>
-      <c r="S29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U29" s="1">
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V29" s="1">
         <v>30</v>
       </c>
-      <c r="V29" s="1">
+      <c r="W29" s="1">
         <v>100</v>
       </c>
-      <c r="W29" s="1">
+      <c r="X29" s="1">
         <v>50</v>
       </c>
-      <c r="X29" s="1">
+      <c r="Y29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:24">
+    <row r="30" ht="15" customHeight="1" spans="1:25">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>101</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3587,17 +3675,17 @@
       <c r="F30" s="1">
         <v>3</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="G30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I30" s="1">
         <v>1926</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
@@ -3606,50 +3694,53 @@
         <v>1</v>
       </c>
       <c r="M30" s="1">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1">
         <v>2002</v>
       </c>
-      <c r="N30" s="1">
-        <v>0</v>
-      </c>
       <c r="O30" s="1">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>0</v>
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R30" s="1">
         <v>0</v>
       </c>
-      <c r="S30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U30" s="1">
+      <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V30" s="1">
         <v>50</v>
       </c>
-      <c r="V30" s="1">
+      <c r="W30" s="1">
         <v>300</v>
       </c>
-      <c r="W30" s="1">
+      <c r="X30" s="1">
         <v>50</v>
       </c>
-      <c r="X30" s="1">
+      <c r="Y30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:24">
+    <row r="31" ht="15" customHeight="1" spans="1:25">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>102</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3657,17 +3748,17 @@
       <c r="F31" s="1">
         <v>3</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="G31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I31" s="1">
         <v>1927</v>
       </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
@@ -3676,50 +3767,53 @@
         <v>1</v>
       </c>
       <c r="M31" s="1">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
         <v>2003</v>
       </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
       <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R31" s="1">
         <v>0</v>
       </c>
-      <c r="S31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U31" s="1">
+      <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V31" s="1">
         <v>50</v>
       </c>
-      <c r="V31" s="1">
+      <c r="W31" s="1">
         <v>300</v>
       </c>
-      <c r="W31" s="1">
+      <c r="X31" s="1">
         <v>50</v>
       </c>
-      <c r="X31" s="1">
+      <c r="Y31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:24">
+    <row r="32" ht="15" customHeight="1" spans="1:25">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>103</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3727,17 +3821,17 @@
       <c r="F32" s="1">
         <v>2</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="G32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I32" s="1">
         <v>1928</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
       <c r="J32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
@@ -3746,50 +3840,53 @@
         <v>1</v>
       </c>
       <c r="M32" s="1">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1">
         <v>2004</v>
       </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
       <c r="O32" s="1">
         <v>0</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R32" s="1">
         <v>0</v>
       </c>
-      <c r="S32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U32" s="1">
+      <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V32" s="1">
         <v>30</v>
       </c>
-      <c r="V32" s="1">
+      <c r="W32" s="1">
         <v>100</v>
       </c>
-      <c r="W32" s="1">
+      <c r="X32" s="1">
         <v>50</v>
       </c>
-      <c r="X32" s="1">
+      <c r="Y32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:24">
+    <row r="33" ht="15" customHeight="1" spans="1:25">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>104</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3797,17 +3894,17 @@
       <c r="F33" s="1">
         <v>3</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H33" s="1">
+      <c r="G33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I33" s="1">
         <v>1929</v>
       </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
@@ -3816,50 +3913,53 @@
         <v>1</v>
       </c>
       <c r="M33" s="1">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1">
         <v>2005</v>
       </c>
-      <c r="N33" s="1">
-        <v>0</v>
-      </c>
       <c r="O33" s="1">
         <v>0</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
       </c>
-      <c r="S33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U33" s="1">
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V33" s="1">
         <v>50</v>
       </c>
-      <c r="V33" s="1">
+      <c r="W33" s="1">
         <v>300</v>
       </c>
-      <c r="W33" s="1">
+      <c r="X33" s="1">
         <v>50</v>
       </c>
-      <c r="X33" s="1">
+      <c r="Y33" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:24">
+    <row r="34" ht="15" customHeight="1" spans="1:25">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>105</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3867,17 +3967,17 @@
       <c r="F34" s="1">
         <v>3</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H34" s="1">
+      <c r="G34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I34" s="1">
         <v>1930</v>
       </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
       <c r="J34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
@@ -3886,50 +3986,53 @@
         <v>1</v>
       </c>
       <c r="M34" s="1">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1">
         <v>2006</v>
       </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
       <c r="O34" s="1">
         <v>0</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>0</v>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
       </c>
-      <c r="S34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U34" s="1">
+      <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V34" s="1">
         <v>50</v>
       </c>
-      <c r="V34" s="1">
+      <c r="W34" s="1">
         <v>300</v>
       </c>
-      <c r="W34" s="1">
+      <c r="X34" s="1">
         <v>50</v>
       </c>
-      <c r="X34" s="1">
+      <c r="Y34" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:24">
+    <row r="35" ht="15" customHeight="1" spans="1:25">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>106</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3937,17 +4040,17 @@
       <c r="F35" s="1">
         <v>2</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H35" s="1">
+      <c r="G35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I35" s="1">
         <v>1931</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
       <c r="J35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
@@ -3956,50 +4059,53 @@
         <v>1</v>
       </c>
       <c r="M35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1">
         <v>2007</v>
       </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>0</v>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R35" s="1">
         <v>0</v>
       </c>
-      <c r="S35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U35" s="1">
+      <c r="S35" s="1">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V35" s="1">
         <v>30</v>
       </c>
-      <c r="V35" s="1">
+      <c r="W35" s="1">
         <v>100</v>
       </c>
-      <c r="W35" s="1">
+      <c r="X35" s="1">
         <v>50</v>
       </c>
-      <c r="X35" s="1">
+      <c r="Y35" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:24">
+    <row r="36" ht="15" customHeight="1" spans="1:25">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>107</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -4007,17 +4113,17 @@
       <c r="F36" s="1">
         <v>2</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H36" s="1">
+      <c r="G36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" s="1">
         <v>1932</v>
       </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
       <c r="J36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
@@ -4026,50 +4132,53 @@
         <v>1</v>
       </c>
       <c r="M36" s="1">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1">
         <v>2008</v>
       </c>
-      <c r="N36" s="1">
-        <v>0</v>
-      </c>
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
       </c>
-      <c r="S36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U36" s="1">
+      <c r="S36" s="1">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V36" s="1">
         <v>30</v>
       </c>
-      <c r="V36" s="1">
+      <c r="W36" s="1">
         <v>100</v>
       </c>
-      <c r="W36" s="1">
+      <c r="X36" s="1">
         <v>50</v>
       </c>
-      <c r="X36" s="1">
+      <c r="Y36" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:24">
+    <row r="37" ht="15" customHeight="1" spans="1:25">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>108</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4077,17 +4186,17 @@
       <c r="F37" s="1">
         <v>2</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H37" s="1">
+      <c r="G37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I37" s="1">
         <v>1933</v>
       </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
       <c r="J37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
@@ -4096,50 +4205,53 @@
         <v>1</v>
       </c>
       <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
         <v>2009</v>
       </c>
-      <c r="N37" s="1">
-        <v>0</v>
-      </c>
       <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>0</v>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
       </c>
-      <c r="S37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U37" s="1">
+      <c r="S37" s="1">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V37" s="1">
         <v>30</v>
       </c>
-      <c r="V37" s="1">
+      <c r="W37" s="1">
         <v>100</v>
       </c>
-      <c r="W37" s="1">
+      <c r="X37" s="1">
         <v>50</v>
       </c>
-      <c r="X37" s="1">
+      <c r="Y37" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:24">
+    <row r="38" ht="15" customHeight="1" spans="1:25">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>109</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4147,17 +4259,17 @@
       <c r="F38" s="1">
         <v>4</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H38" s="1">
+      <c r="G38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I38" s="1">
         <v>1934</v>
       </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
       <c r="J38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
@@ -4166,50 +4278,53 @@
         <v>1</v>
       </c>
       <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
         <v>2010</v>
       </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
       <c r="O38" s="1">
         <v>0</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U38" s="1">
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V38" s="1">
         <v>100</v>
       </c>
-      <c r="V38" s="1">
+      <c r="W38" s="1">
         <v>800</v>
       </c>
-      <c r="W38" s="1">
+      <c r="X38" s="1">
         <v>50</v>
       </c>
-      <c r="X38" s="1">
+      <c r="Y38" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:24">
+    <row r="39" ht="15" customHeight="1" spans="1:25">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>110</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4217,17 +4332,17 @@
       <c r="F39" s="1">
         <v>3</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" s="1">
+      <c r="G39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I39" s="1">
         <v>1935</v>
       </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
       <c r="J39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
@@ -4236,50 +4351,53 @@
         <v>1</v>
       </c>
       <c r="M39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1">
         <v>2011</v>
       </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
       <c r="O39" s="1">
         <v>0</v>
       </c>
-      <c r="P39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0</v>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
       </c>
-      <c r="S39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U39" s="1">
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V39" s="1">
         <v>50</v>
       </c>
-      <c r="V39" s="1">
+      <c r="W39" s="1">
         <v>300</v>
       </c>
-      <c r="W39" s="1">
+      <c r="X39" s="1">
         <v>50</v>
       </c>
-      <c r="X39" s="1">
+      <c r="Y39" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:24">
+    <row r="40" ht="15" customHeight="1" spans="1:25">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>111</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4287,17 +4405,17 @@
       <c r="F40" s="1">
         <v>4</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H40" s="1">
+      <c r="G40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I40" s="1">
         <v>1936</v>
       </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
       <c r="J40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
         <v>1</v>
@@ -4306,50 +4424,53 @@
         <v>1</v>
       </c>
       <c r="M40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1">
         <v>2012</v>
       </c>
-      <c r="N40" s="1">
-        <v>0</v>
-      </c>
       <c r="O40" s="1">
         <v>0</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0</v>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
       </c>
-      <c r="S40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U40" s="1">
+      <c r="S40" s="1">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V40" s="1">
         <v>100</v>
       </c>
-      <c r="V40" s="1">
+      <c r="W40" s="1">
         <v>800</v>
       </c>
-      <c r="W40" s="1">
+      <c r="X40" s="1">
         <v>50</v>
       </c>
-      <c r="X40" s="1">
+      <c r="Y40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:24">
+    <row r="41" ht="15" customHeight="1" spans="1:25">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>112</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4357,17 +4478,17 @@
       <c r="F41" s="1">
         <v>2</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H41" s="1">
+      <c r="G41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I41" s="1">
         <v>1937</v>
       </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
       <c r="J41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
         <v>1</v>
@@ -4376,50 +4497,53 @@
         <v>1</v>
       </c>
       <c r="M41" s="1">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1">
         <v>2013</v>
       </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
       <c r="O41" s="1">
         <v>0</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>0</v>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R41" s="1">
         <v>0</v>
       </c>
-      <c r="S41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U41" s="1">
+      <c r="S41" s="1">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V41" s="1">
         <v>30</v>
       </c>
-      <c r="V41" s="1">
+      <c r="W41" s="1">
         <v>100</v>
       </c>
-      <c r="W41" s="1">
+      <c r="X41" s="1">
         <v>50</v>
       </c>
-      <c r="X41" s="1">
+      <c r="Y41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:24">
+    <row r="42" ht="15" customHeight="1" spans="1:25">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>113</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4427,17 +4551,17 @@
       <c r="F42" s="1">
         <v>3</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H42" s="1">
+      <c r="G42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I42" s="1">
         <v>1938</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
       <c r="J42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
@@ -4446,50 +4570,53 @@
         <v>1</v>
       </c>
       <c r="M42" s="1">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1">
         <v>2014</v>
       </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="P42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>0</v>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R42" s="1">
         <v>0</v>
       </c>
-      <c r="S42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U42" s="1">
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V42" s="1">
         <v>50</v>
       </c>
-      <c r="V42" s="1">
+      <c r="W42" s="1">
         <v>300</v>
       </c>
-      <c r="W42" s="1">
+      <c r="X42" s="1">
         <v>50</v>
       </c>
-      <c r="X42" s="1">
+      <c r="Y42" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:24">
+    <row r="43" ht="15" customHeight="1" spans="1:25">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>114</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -4497,17 +4624,17 @@
       <c r="F43" s="1">
         <v>3</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H43" s="1">
+      <c r="G43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I43" s="1">
         <v>1939</v>
       </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
       <c r="J43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
@@ -4516,50 +4643,53 @@
         <v>1</v>
       </c>
       <c r="M43" s="1">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1">
         <v>2015</v>
       </c>
-      <c r="N43" s="1">
-        <v>0</v>
-      </c>
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>0</v>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
       </c>
-      <c r="S43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U43" s="1">
+      <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V43" s="1">
         <v>50</v>
       </c>
-      <c r="V43" s="1">
+      <c r="W43" s="1">
         <v>300</v>
       </c>
-      <c r="W43" s="1">
+      <c r="X43" s="1">
         <v>50</v>
       </c>
-      <c r="X43" s="1">
+      <c r="Y43" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:24">
+    <row r="44" ht="15" customHeight="1" spans="1:25">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>115</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4567,17 +4697,17 @@
       <c r="F44" s="1">
         <v>3</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H44" s="1">
+      <c r="G44" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I44" s="1">
         <v>1940</v>
       </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
       <c r="J44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
@@ -4586,50 +4716,53 @@
         <v>1</v>
       </c>
       <c r="M44" s="1">
+        <v>1</v>
+      </c>
+      <c r="N44" s="1">
         <v>2016</v>
       </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="P44" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
       </c>
-      <c r="S44" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U44" s="1">
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V44" s="1">
         <v>50</v>
       </c>
-      <c r="V44" s="1">
+      <c r="W44" s="1">
         <v>300</v>
       </c>
-      <c r="W44" s="1">
+      <c r="X44" s="1">
         <v>50</v>
       </c>
-      <c r="X44" s="1">
+      <c r="Y44" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:24">
+    <row r="45" ht="15" customHeight="1" spans="1:25">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>116</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4637,17 +4770,17 @@
       <c r="F45" s="1">
         <v>3</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H45" s="1">
+      <c r="G45" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I45" s="1">
         <v>1941</v>
       </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
       <c r="J45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
@@ -4656,50 +4789,53 @@
         <v>1</v>
       </c>
       <c r="M45" s="1">
+        <v>1</v>
+      </c>
+      <c r="N45" s="1">
         <v>2017</v>
       </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
       <c r="O45" s="1">
         <v>0</v>
       </c>
-      <c r="P45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>0</v>
+      <c r="P45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R45" s="1">
         <v>0</v>
       </c>
-      <c r="S45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U45" s="1">
+      <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V45" s="1">
         <v>50</v>
       </c>
-      <c r="V45" s="1">
+      <c r="W45" s="1">
         <v>300</v>
       </c>
-      <c r="W45" s="1">
+      <c r="X45" s="1">
         <v>50</v>
       </c>
-      <c r="X45" s="1">
+      <c r="Y45" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:24">
+    <row r="46" ht="15" customHeight="1" spans="1:25">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>117</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -4707,17 +4843,17 @@
       <c r="F46" s="1">
         <v>3</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H46" s="1">
+      <c r="G46" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I46" s="1">
         <v>1942</v>
       </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
       <c r="J46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
         <v>1</v>
@@ -4726,50 +4862,53 @@
         <v>1</v>
       </c>
       <c r="M46" s="1">
+        <v>1</v>
+      </c>
+      <c r="N46" s="1">
         <v>2018</v>
       </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R46" s="1">
         <v>0</v>
       </c>
-      <c r="S46" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U46" s="1">
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V46" s="1">
         <v>50</v>
       </c>
-      <c r="V46" s="1">
+      <c r="W46" s="1">
         <v>300</v>
       </c>
-      <c r="W46" s="1">
+      <c r="X46" s="1">
         <v>50</v>
       </c>
-      <c r="X46" s="1">
+      <c r="Y46" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:24">
+    <row r="47" ht="15" customHeight="1" spans="1:25">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>118</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4777,17 +4916,17 @@
       <c r="F47" s="1">
         <v>3</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H47" s="1">
+      <c r="G47" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I47" s="1">
         <v>1943</v>
       </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
@@ -4796,50 +4935,53 @@
         <v>1</v>
       </c>
       <c r="M47" s="1">
+        <v>1</v>
+      </c>
+      <c r="N47" s="1">
         <v>2019</v>
       </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="P47" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>0</v>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
       </c>
-      <c r="S47" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U47" s="1">
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V47" s="1">
         <v>50</v>
       </c>
-      <c r="V47" s="1">
+      <c r="W47" s="1">
         <v>300</v>
       </c>
-      <c r="W47" s="1">
+      <c r="X47" s="1">
         <v>50</v>
       </c>
-      <c r="X47" s="1">
+      <c r="Y47" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:24">
+    <row r="48" ht="15" customHeight="1" spans="1:25">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>119</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4847,17 +4989,17 @@
       <c r="F48" s="1">
         <v>3</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H48" s="1">
+      <c r="G48" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I48" s="1">
         <v>1944</v>
       </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
@@ -4866,50 +5008,53 @@
         <v>1</v>
       </c>
       <c r="M48" s="1">
+        <v>1</v>
+      </c>
+      <c r="N48" s="1">
         <v>2020</v>
       </c>
-      <c r="N48" s="1">
-        <v>0</v>
-      </c>
       <c r="O48" s="1">
         <v>0</v>
       </c>
-      <c r="P48" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q48" s="1">
-        <v>0</v>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R48" s="1">
         <v>0</v>
       </c>
-      <c r="S48" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T48" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U48" s="1">
+      <c r="S48" s="1">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V48" s="1">
         <v>50</v>
       </c>
-      <c r="V48" s="1">
+      <c r="W48" s="1">
         <v>300</v>
       </c>
-      <c r="W48" s="1">
+      <c r="X48" s="1">
         <v>50</v>
       </c>
-      <c r="X48" s="1">
+      <c r="Y48" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:24">
+    <row r="49" ht="15" customHeight="1" spans="1:25">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>120</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -4917,17 +5062,17 @@
       <c r="F49" s="1">
         <v>2</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" s="1">
+      <c r="G49" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I49" s="1">
         <v>1945</v>
       </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
         <v>1</v>
@@ -4936,50 +5081,53 @@
         <v>1</v>
       </c>
       <c r="M49" s="1">
+        <v>1</v>
+      </c>
+      <c r="N49" s="1">
         <v>2021</v>
       </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>0</v>
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R49" s="1">
         <v>0</v>
       </c>
-      <c r="S49" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U49" s="1">
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V49" s="1">
         <v>30</v>
       </c>
-      <c r="V49" s="1">
+      <c r="W49" s="1">
         <v>100</v>
       </c>
-      <c r="W49" s="1">
+      <c r="X49" s="1">
         <v>50</v>
       </c>
-      <c r="X49" s="1">
+      <c r="Y49" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:24">
+    <row r="50" ht="15" customHeight="1" spans="1:25">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>121</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -4987,17 +5135,17 @@
       <c r="F50" s="1">
         <v>3</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H50" s="1">
+      <c r="G50" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I50" s="1">
         <v>1946</v>
       </c>
-      <c r="I50" s="1">
-        <v>0</v>
-      </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
         <v>1</v>
@@ -5006,50 +5154,53 @@
         <v>1</v>
       </c>
       <c r="M50" s="1">
+        <v>1</v>
+      </c>
+      <c r="N50" s="1">
         <v>2022</v>
       </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>0</v>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R50" s="1">
         <v>0</v>
       </c>
-      <c r="S50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T50" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U50" s="1">
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V50" s="1">
         <v>50</v>
       </c>
-      <c r="V50" s="1">
+      <c r="W50" s="1">
         <v>300</v>
       </c>
-      <c r="W50" s="1">
+      <c r="X50" s="1">
         <v>50</v>
       </c>
-      <c r="X50" s="1">
+      <c r="Y50" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:24">
+    <row r="51" ht="15" customHeight="1" spans="1:25">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>122</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -5057,17 +5208,17 @@
       <c r="F51" s="1">
         <v>2</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H51" s="1">
+      <c r="G51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I51" s="1">
         <v>1947</v>
       </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
       <c r="J51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
         <v>1</v>
@@ -5076,50 +5227,53 @@
         <v>1</v>
       </c>
       <c r="M51" s="1">
+        <v>1</v>
+      </c>
+      <c r="N51" s="1">
         <v>2023</v>
       </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
       <c r="O51" s="1">
         <v>0</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>0</v>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
       </c>
-      <c r="S51" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U51" s="1">
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V51" s="1">
         <v>30</v>
       </c>
-      <c r="V51" s="1">
+      <c r="W51" s="1">
         <v>100</v>
       </c>
-      <c r="W51" s="1">
+      <c r="X51" s="1">
         <v>50</v>
       </c>
-      <c r="X51" s="1">
+      <c r="Y51" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:24">
+    <row r="52" ht="15" customHeight="1" spans="1:25">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>123</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -5127,17 +5281,17 @@
       <c r="F52" s="1">
         <v>2</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H52" s="1">
+      <c r="G52" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I52" s="1">
         <v>1948</v>
       </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
       <c r="J52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
         <v>1</v>
@@ -5146,50 +5300,53 @@
         <v>1</v>
       </c>
       <c r="M52" s="1">
+        <v>1</v>
+      </c>
+      <c r="N52" s="1">
         <v>2024</v>
       </c>
-      <c r="N52" s="1">
-        <v>0</v>
-      </c>
       <c r="O52" s="1">
         <v>0</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>0</v>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R52" s="1">
         <v>0</v>
       </c>
-      <c r="S52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U52" s="1">
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V52" s="1">
         <v>30</v>
       </c>
-      <c r="V52" s="1">
+      <c r="W52" s="1">
         <v>100</v>
       </c>
-      <c r="W52" s="1">
+      <c r="X52" s="1">
         <v>50</v>
       </c>
-      <c r="X52" s="1">
+      <c r="Y52" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:24">
+    <row r="53" ht="15" customHeight="1" spans="1:25">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>999</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E53" s="1">
         <v>5</v>
@@ -5197,24 +5354,24 @@
       <c r="F53" s="1">
         <v>1</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H53" s="1">
+      <c r="G53" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I53" s="1">
         <v>1101</v>
       </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
       <c r="J53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1">
         <v>999999999</v>
       </c>
-      <c r="L53" s="1">
-        <v>0</v>
-      </c>
       <c r="M53" s="1">
         <v>0</v>
       </c>
@@ -5224,42 +5381,45 @@
       <c r="O53" s="1">
         <v>0</v>
       </c>
-      <c r="P53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0</v>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R53" s="1">
         <v>0</v>
       </c>
-      <c r="S53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U53" s="1">
-        <v>0</v>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="V53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="1">
         <v>0</v>
       </c>
+      <c r="Y53" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:24">
+    <row r="54" ht="15" customHeight="1" spans="1:25">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>9999</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E54" s="1">
         <v>5</v>
@@ -5267,24 +5427,24 @@
       <c r="F54" s="1">
         <v>4</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H54" s="1">
+      <c r="G54" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I54" s="1">
         <v>1102</v>
       </c>
-      <c r="I54" s="1">
-        <v>0</v>
-      </c>
       <c r="J54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1">
         <v>999999999</v>
       </c>
-      <c r="L54" s="1">
-        <v>0</v>
-      </c>
       <c r="M54" s="1">
         <v>0</v>
       </c>
@@ -5294,42 +5454,45 @@
       <c r="O54" s="1">
         <v>0</v>
       </c>
-      <c r="P54" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>0</v>
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
       </c>
-      <c r="S54" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U54" s="1">
-        <v>0</v>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
         <v>999</v>
       </c>
-      <c r="W54" s="1">
-        <v>0</v>
-      </c>
       <c r="X54" s="1">
         <v>0</v>
       </c>
+      <c r="Y54" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:24">
+    <row r="55" ht="15" customHeight="1" spans="1:25">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>99999</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E55" s="1">
         <v>5</v>
@@ -5337,24 +5500,24 @@
       <c r="F55" s="1">
         <v>3</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H55" s="1">
+      <c r="G55" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I55" s="1">
         <v>1103</v>
       </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
       <c r="J55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
         <v>999999999</v>
       </c>
-      <c r="L55" s="1">
-        <v>0</v>
-      </c>
       <c r="M55" s="1">
         <v>0</v>
       </c>
@@ -5364,23 +5527,23 @@
       <c r="O55" s="1">
         <v>0</v>
       </c>
-      <c r="P55" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>0</v>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="R55" s="1">
         <v>0</v>
       </c>
-      <c r="S55" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U55" s="1">
-        <v>0</v>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="V55" s="1">
         <v>0</v>
@@ -5389,6 +5552,9 @@
         <v>0</v>
       </c>
       <c r="X55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="1">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="132">
   <si>
     <t>#</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Quality</t>
+    <t>Rarity</t>
   </si>
   <si>
     <t>IsOnlyInGame</t>
@@ -56,42 +56,12 @@
     <t>IconId</t>
   </si>
   <si>
-    <t>DetailIconId</t>
-  </si>
-  <si>
     <t>CanStack</t>
   </si>
   <si>
     <t>MaxStackCount</t>
   </si>
   <si>
-    <t>CanUse</t>
-  </si>
-  <si>
-    <t>UseEffectId</t>
-  </si>
-  <si>
-    <t>CanEquip</t>
-  </si>
-  <si>
-    <t>SpecialEffectId</t>
-  </si>
-  <si>
-    <t>AffixPoolIds</t>
-  </si>
-  <si>
-    <t>AffixMinCount</t>
-  </si>
-  <si>
-    <t>AffixMaxCount</t>
-  </si>
-  <si>
-    <t>SynergyIds</t>
-  </si>
-  <si>
-    <t>BaseAttributes</t>
-  </si>
-  <si>
     <t>SellPrice</t>
   </si>
   <si>
@@ -101,9 +71,6 @@
     <t>Weight</t>
   </si>
   <si>
-    <t>MaxDurability</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -113,9 +80,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>物品ID</t>
   </si>
   <si>
@@ -137,10 +101,7 @@
     <t>物品描述</t>
   </si>
   <si>
-    <t>缩略图资源ID</t>
-  </si>
-  <si>
-    <t>详细图资源ID</t>
+    <t>图标资源ID</t>
   </si>
   <si>
     <t>是否可堆叠</t>
@@ -149,54 +110,21 @@
     <t>最大堆叠数</t>
   </si>
   <si>
-    <t>是否可使用</t>
-  </si>
-  <si>
-    <t>使用效果ID</t>
-  </si>
-  <si>
-    <t>是否可装备</t>
-  </si>
-  <si>
-    <t>特殊效果ID</t>
-  </si>
-  <si>
-    <t>词条池ID列表</t>
-  </si>
-  <si>
-    <t>词条最小数量</t>
-  </si>
-  <si>
-    <t>词条最大数量</t>
-  </si>
-  <si>
-    <t>羁绊ID列表</t>
-  </si>
-  <si>
-    <t>基础属性(JSON格式)</t>
-  </si>
-  <si>
     <t>售价</t>
   </si>
   <si>
+    <t>价值</t>
+  </si>
+  <si>
     <t>重量(克)</t>
   </si>
   <si>
-    <t>最大耐久度</t>
-  </si>
-  <si>
     <t>钱包</t>
   </si>
   <si>
     <t>使用后随机获得100-500金币</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>生命药水</t>
   </si>
   <si>
@@ -233,196 +161,106 @@
     <t>传说中的三神器之一，蕴含神秘力量</t>
   </si>
   <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>{"MaxHP":"500","CritRate":"15%"}</t>
-  </si>
-  <si>
     <t>天丛云剑</t>
   </si>
   <si>
     <t>传说中的三神器之一，削铁如泥</t>
   </si>
   <si>
-    <t>{"Attack":"200","CritDamage":"50%"}</t>
-  </si>
-  <si>
     <t>八咫镜</t>
   </si>
   <si>
     <t>传说中的三神器之一，可以反射一切</t>
   </si>
   <si>
-    <t>{"Defense":"300","DamageReduction":"20%"}</t>
-  </si>
-  <si>
     <t>石中剑</t>
   </si>
   <si>
     <t>传说中的圣剑，只有王者才能拔出</t>
   </si>
   <si>
-    <t>2001,2003</t>
-  </si>
-  <si>
-    <t>{"Attack":"60","CritRate":"10%"}</t>
-  </si>
-  <si>
     <t>龙鳞铠甲</t>
   </si>
   <si>
     <t>由巨龙鳞片打造的铠甲</t>
   </si>
   <si>
-    <t>2002,2006</t>
-  </si>
-  <si>
-    <t>{"MaxHP":"200","Defense":"50"}</t>
-  </si>
-  <si>
     <t>精灵之戒</t>
   </si>
   <si>
     <t>精灵族的传家宝</t>
   </si>
   <si>
-    <t>2004,2005</t>
-  </si>
-  <si>
-    <t>{"MoveSpeed":"15%","Evasion":"10%"}</t>
-  </si>
-  <si>
     <t>月华玉璧</t>
   </si>
   <si>
     <t>月神赐予的古老玉璧，蕴含月华之力，可反射一切邪恶</t>
   </si>
   <si>
-    <t>5001</t>
-  </si>
-  <si>
-    <t>{"Defense":"400","MagicResist":"25%","CritReduction":"20%"}</t>
-  </si>
-  <si>
     <t>太阴弦月弓</t>
   </si>
   <si>
     <t>月神的弓，弦如弦月般优雅，箭矢蕴含月光之力</t>
   </si>
   <si>
-    <t>{"Attack":"350","CritRate":"25%","Evasion":"15%"}</t>
-  </si>
-  <si>
     <t>月轮镜</t>
   </si>
   <si>
     <t>月神的镜子，能够照亮黑暗，反射月光</t>
   </si>
   <si>
-    <t>{"MagicPower":"300","MagicResist":"30%","Regeneration":"8%"}</t>
-  </si>
-  <si>
     <t>炎魔之心</t>
   </si>
   <si>
     <t>炎魔的心脏，跳动着永恒的火焰</t>
   </si>
   <si>
-    <t>5002</t>
-  </si>
-  <si>
-    <t>{"MaxHP":"500","LifeSteal":"20%","FireDamage":"30%"}</t>
-  </si>
-  <si>
     <t>炎魔之冠</t>
   </si>
   <si>
     <t>炎魔的王冠，象征权力与统治</t>
   </si>
   <si>
-    <t>{"Attack":"400","CritDamage":"50%","Leadership":"15%"}</t>
-  </si>
-  <si>
     <t>炎魔之剑</t>
   </si>
   <si>
     <t>炎魔的剑，剑身燃烧着永恒的火焰</t>
   </si>
   <si>
-    <t>{"Attack":"380","FireDamage":"25%","AttackSpeed":"15%"}</t>
-  </si>
-  <si>
     <t>古剑·樱花落</t>
   </si>
   <si>
     <t>樱花盛开时锻造的古剑，剑身如樱花般优雅，却有致命的锋芒</t>
   </si>
   <si>
-    <t>2007,2008</t>
-  </si>
-  <si>
-    <t>{"Attack":"150","CritRate":"20%","Evasion":"8%"}</t>
-  </si>
-  <si>
     <t>暗影斗篷</t>
   </si>
   <si>
     <t>用暗影魔法编织的斗篷，能够隐匿身形，融入黑暗</t>
   </si>
   <si>
-    <t>2009,2010</t>
-  </si>
-  <si>
-    <t>{"Defense":"80","Evasion":"15%","MagicResist":"15%"}</t>
-  </si>
-  <si>
     <t>圣光铠甲</t>
   </si>
   <si>
     <t>被圣光祝福的铠甲，闪烁着神圣的光芒，能够保护穿戴者免受邪恶</t>
   </si>
   <si>
-    <t>2011,2012</t>
-  </si>
-  <si>
-    <t>{"Defense":"200","MagicResist":"30%","HealthRegen":"3%"}</t>
-  </si>
-  <si>
     <t>古墓盗贼手套</t>
   </si>
   <si>
     <t>从古墓中发现的神秘手套，能够增强手指的灵活性和力量</t>
   </si>
   <si>
-    <t>2013,2014</t>
-  </si>
-  <si>
-    <t>{"Attack":"80","AttackSpeed":"15%","CritRate":"10%"}</t>
-  </si>
-  <si>
     <t>冰晶靴</t>
   </si>
   <si>
     <t>用冰晶魔法制成的靴子，能够在冰面上快速移动，冻结敌人</t>
   </si>
   <si>
-    <t>2015,2016</t>
-  </si>
-  <si>
-    <t>{"MoveSpeed":"20%","Defense":"60","CooldownReduction":"10%"}</t>
-  </si>
-  <si>
     <t>风暴法杖</t>
   </si>
   <si>
     <t>由风元素凝聚而成的法杖，顶端闪烁着雷电光芒，能够召唤风暴之力</t>
-  </si>
-  <si>
-    <t>2017,2018</t>
-  </si>
-  <si>
-    <t>{"MagicPower":"200","CooldownReduction":"15%","AttackSpeed":"10%"}</t>
   </si>
   <si>
     <t>卡牌-神圣庇护</t>
@@ -597,7 +435,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1053,157 +898,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1552,7 +1394,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1560,26 +1402,16 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="50" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="10" customWidth="1"/>
-    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,19 +1430,8 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1651,198 +1472,101 @@
       <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:14">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1854,68 +1578,35 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I5" s="1">
         <v>1901</v>
       </c>
-      <c r="J5" s="1">
-        <v>0</v>
+      <c r="J5" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="L5" s="1">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="M5" s="1">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="N5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V5" s="1">
-        <v>50</v>
-      </c>
-      <c r="W5" s="1">
-        <v>120</v>
-      </c>
-      <c r="X5" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:14">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1927,68 +1618,35 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="I6" s="1">
         <v>1902</v>
       </c>
-      <c r="J6" s="1">
-        <v>0</v>
+      <c r="J6" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="L6" s="1">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="N6" s="1">
-        <v>1002</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" s="1">
-        <v>10</v>
-      </c>
-      <c r="W6" s="1">
-        <v>40</v>
-      </c>
-      <c r="X6" s="1">
         <v>100</v>
       </c>
-      <c r="Y6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:14">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2000,68 +1658,35 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1">
         <v>1903</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="L7" s="1">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="M7" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="N7" s="1">
-        <v>1003</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V7" s="1">
-        <v>10</v>
-      </c>
-      <c r="W7" s="1">
-        <v>40</v>
-      </c>
-      <c r="X7" s="1">
         <v>100</v>
       </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:14">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2073,68 +1698,35 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I8" s="1">
         <v>1904</v>
       </c>
-      <c r="J8" s="1">
-        <v>0</v>
+      <c r="J8" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L8" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M8" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N8" s="1">
-        <v>1004</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V8" s="1">
-        <v>100</v>
-      </c>
-      <c r="W8" s="1">
-        <v>300</v>
-      </c>
-      <c r="X8" s="1">
         <v>200</v>
       </c>
-      <c r="Y8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:14">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -2146,68 +1738,35 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I9" s="1">
         <v>1905</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0</v>
-      </c>
-      <c r="W9" s="1">
-        <v>800</v>
-      </c>
-      <c r="X9" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:14">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2219,68 +1778,35 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1">
         <v>1906</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V10" s="1">
-        <v>0</v>
-      </c>
-      <c r="W10" s="1">
-        <v>800</v>
-      </c>
-      <c r="X10" s="1">
         <v>30</v>
       </c>
-      <c r="Y10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:14">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2292,68 +1818,35 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="I11" s="1">
         <v>1907</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>1</v>
-      </c>
-      <c r="P11" s="1">
-        <v>3001</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="V11" s="1">
-        <v>0</v>
-      </c>
-      <c r="W11" s="1">
-        <v>800</v>
-      </c>
-      <c r="X11" s="1">
         <v>500</v>
       </c>
-      <c r="Y11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:14">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -2365,68 +1858,35 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="I12" s="1">
         <v>1908</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>3002</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
-      <c r="W12" s="1">
         <v>800</v>
       </c>
-      <c r="X12" s="1">
-        <v>800</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:14">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -2438,68 +1898,35 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="I13" s="1">
         <v>1909</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1">
-        <v>3003</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="V13" s="1">
-        <v>0</v>
-      </c>
-      <c r="W13" s="1">
-        <v>800</v>
-      </c>
-      <c r="X13" s="1">
         <v>600</v>
       </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:14">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -2511,68 +1938,35 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="I14" s="1">
         <v>1910</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>1</v>
-      </c>
-      <c r="P14" s="1">
-        <v>4001</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="R14" s="1">
-        <v>2</v>
-      </c>
-      <c r="S14" s="1">
-        <v>3</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="V14" s="1">
-        <v>500</v>
-      </c>
-      <c r="W14" s="1">
-        <v>800</v>
-      </c>
-      <c r="X14" s="1">
         <v>700</v>
       </c>
-      <c r="Y14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:14">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -2584,68 +1978,35 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="I15" s="1">
         <v>1911</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
-      <c r="P15" s="1">
-        <v>4002</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R15" s="1">
-        <v>2</v>
-      </c>
-      <c r="S15" s="1">
-        <v>3</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="V15" s="1">
-        <v>500</v>
-      </c>
-      <c r="W15" s="1">
-        <v>800</v>
-      </c>
-      <c r="X15" s="1">
         <v>1200</v>
       </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:14">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2657,68 +2018,35 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="I16" s="1">
         <v>1912</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>1</v>
-      </c>
-      <c r="P16" s="1">
-        <v>4003</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R16" s="1">
-        <v>1</v>
-      </c>
-      <c r="S16" s="1">
-        <v>2</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V16" s="1">
-        <v>300</v>
-      </c>
-      <c r="W16" s="1">
-        <v>500</v>
-      </c>
-      <c r="X16" s="1">
         <v>100</v>
       </c>
-      <c r="Y16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:14">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -2730,68 +2058,35 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="I17" s="1">
         <v>1913</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1</v>
-      </c>
-      <c r="P17" s="1">
-        <v>5001</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>800</v>
-      </c>
-      <c r="X17" s="1">
         <v>500</v>
       </c>
-      <c r="Y17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:14">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -2803,68 +2098,35 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="I18" s="1">
         <v>1914</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="O18" s="1">
-        <v>1</v>
-      </c>
-      <c r="P18" s="1">
-        <v>5002</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="V18" s="1">
-        <v>0</v>
-      </c>
-      <c r="W18" s="1">
         <v>800</v>
       </c>
-      <c r="X18" s="1">
-        <v>800</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:14">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>15</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2876,68 +2138,35 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="I19" s="1">
         <v>1915</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
-      </c>
-      <c r="O19" s="1">
-        <v>1</v>
-      </c>
-      <c r="P19" s="1">
-        <v>5003</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
-      <c r="W19" s="1">
-        <v>800</v>
-      </c>
-      <c r="X19" s="1">
         <v>600</v>
       </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:14">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -2949,68 +2178,35 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="I20" s="1">
         <v>1916</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>1</v>
-      </c>
-      <c r="P20" s="1">
-        <v>5004</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="V20" s="1">
-        <v>0</v>
-      </c>
-      <c r="W20" s="1">
-        <v>800</v>
-      </c>
-      <c r="X20" s="1">
         <v>500</v>
       </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:14">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>17</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -3022,68 +2218,35 @@
         <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="I21" s="1">
         <v>1917</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>1</v>
-      </c>
-      <c r="P21" s="1">
-        <v>5005</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="1">
         <v>800</v>
       </c>
-      <c r="X21" s="1">
-        <v>800</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:14">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -3095,68 +2258,35 @@
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="I22" s="1">
         <v>1918</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>1</v>
-      </c>
-      <c r="P22" s="1">
-        <v>5006</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="1">
-        <v>800</v>
-      </c>
-      <c r="X22" s="1">
         <v>700</v>
       </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:14">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>19</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="E23" s="1">
         <v>4</v>
@@ -3168,68 +2298,35 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="I23" s="1">
         <v>1919</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="1">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>1</v>
-      </c>
-      <c r="P23" s="1">
-        <v>6001</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="R23" s="1">
-        <v>2</v>
-      </c>
-      <c r="S23" s="1">
-        <v>3</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="V23" s="1">
-        <v>600</v>
-      </c>
-      <c r="W23" s="1">
-        <v>1000</v>
-      </c>
-      <c r="X23" s="1">
         <v>700</v>
       </c>
-      <c r="Y23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:14">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -3241,68 +2338,35 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="I24" s="1">
         <v>1920</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N24" s="1">
-        <v>0</v>
-      </c>
-      <c r="O24" s="1">
-        <v>1</v>
-      </c>
-      <c r="P24" s="1">
-        <v>6002</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="R24" s="1">
-        <v>2</v>
-      </c>
-      <c r="S24" s="1">
-        <v>3</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="V24" s="1">
-        <v>400</v>
-      </c>
-      <c r="W24" s="1">
-        <v>700</v>
-      </c>
-      <c r="X24" s="1">
         <v>500</v>
       </c>
-      <c r="Y24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:14">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>21</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3314,68 +2378,35 @@
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="I25" s="1">
         <v>1921</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="1">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="M25" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>1</v>
-      </c>
-      <c r="P25" s="1">
-        <v>6003</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="R25" s="1">
-        <v>2</v>
-      </c>
-      <c r="S25" s="1">
-        <v>3</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="V25" s="1">
-        <v>600</v>
-      </c>
-      <c r="W25" s="1">
-        <v>1000</v>
-      </c>
-      <c r="X25" s="1">
         <v>1200</v>
       </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:14">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>22</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
@@ -3387,68 +2418,35 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="I26" s="1">
         <v>1922</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="1">
-        <v>1</v>
-      </c>
-      <c r="P26" s="1">
-        <v>6004</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="R26" s="1">
-        <v>2</v>
-      </c>
-      <c r="S26" s="1">
-        <v>3</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="V26" s="1">
-        <v>400</v>
-      </c>
-      <c r="W26" s="1">
-        <v>700</v>
-      </c>
-      <c r="X26" s="1">
         <v>300</v>
       </c>
-      <c r="Y26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:14">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>23</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
@@ -3460,68 +2458,35 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="I27" s="1">
         <v>1923</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>1</v>
-      </c>
-      <c r="P27" s="1">
-        <v>6005</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="R27" s="1">
-        <v>2</v>
-      </c>
-      <c r="S27" s="1">
-        <v>3</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="V27" s="1">
         <v>400</v>
       </c>
-      <c r="W27" s="1">
-        <v>700</v>
-      </c>
-      <c r="X27" s="1">
-        <v>400</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:14">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>24</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -3533,68 +2498,35 @@
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="I28" s="1">
         <v>1924</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
-      </c>
-      <c r="O28" s="1">
-        <v>1</v>
-      </c>
-      <c r="P28" s="1">
-        <v>6006</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="R28" s="1">
-        <v>2</v>
-      </c>
-      <c r="S28" s="1">
-        <v>3</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="V28" s="1">
         <v>600</v>
       </c>
-      <c r="W28" s="1">
-        <v>1000</v>
-      </c>
-      <c r="X28" s="1">
-        <v>600</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:14">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>100</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3606,68 +2538,35 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="I29" s="1">
         <v>1925</v>
       </c>
-      <c r="J29" s="1">
-        <v>0</v>
+      <c r="J29" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M29" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N29" s="1">
-        <v>2001</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1">
-        <v>0</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V29" s="1">
-        <v>30</v>
-      </c>
-      <c r="W29" s="1">
-        <v>100</v>
-      </c>
-      <c r="X29" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:14">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>101</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3679,68 +2578,35 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="I30" s="1">
         <v>1926</v>
       </c>
-      <c r="J30" s="1">
-        <v>0</v>
+      <c r="J30" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M30" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N30" s="1">
-        <v>2002</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
-      <c r="S30" s="1">
-        <v>0</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V30" s="1">
-        <v>50</v>
-      </c>
-      <c r="W30" s="1">
-        <v>300</v>
-      </c>
-      <c r="X30" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:14">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>102</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3752,68 +2618,35 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="I31" s="1">
         <v>1927</v>
       </c>
-      <c r="J31" s="1">
-        <v>0</v>
+      <c r="J31" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M31" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N31" s="1">
-        <v>2003</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V31" s="1">
-        <v>50</v>
-      </c>
-      <c r="W31" s="1">
-        <v>300</v>
-      </c>
-      <c r="X31" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:14">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>103</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3825,68 +2658,35 @@
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="I32" s="1">
         <v>1928</v>
       </c>
-      <c r="J32" s="1">
-        <v>0</v>
+      <c r="J32" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M32" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N32" s="1">
-        <v>2004</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1">
-        <v>0</v>
-      </c>
-      <c r="T32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V32" s="1">
-        <v>30</v>
-      </c>
-      <c r="W32" s="1">
-        <v>100</v>
-      </c>
-      <c r="X32" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:14">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>104</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3898,68 +2698,35 @@
         <v>0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="I33" s="1">
         <v>1929</v>
       </c>
-      <c r="J33" s="1">
-        <v>0</v>
+      <c r="J33" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M33" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N33" s="1">
-        <v>2005</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V33" s="1">
-        <v>50</v>
-      </c>
-      <c r="W33" s="1">
-        <v>300</v>
-      </c>
-      <c r="X33" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:14">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>105</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3971,68 +2738,35 @@
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="I34" s="1">
         <v>1930</v>
       </c>
-      <c r="J34" s="1">
-        <v>0</v>
+      <c r="J34" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M34" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N34" s="1">
-        <v>2006</v>
-      </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V34" s="1">
-        <v>50</v>
-      </c>
-      <c r="W34" s="1">
-        <v>300</v>
-      </c>
-      <c r="X34" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:14">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>106</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4044,68 +2778,35 @@
         <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="I35" s="1">
         <v>1931</v>
       </c>
-      <c r="J35" s="1">
-        <v>0</v>
+      <c r="J35" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M35" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N35" s="1">
-        <v>2007</v>
-      </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V35" s="1">
-        <v>30</v>
-      </c>
-      <c r="W35" s="1">
-        <v>100</v>
-      </c>
-      <c r="X35" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:14">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>107</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -4117,68 +2818,35 @@
         <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="I36" s="1">
         <v>1932</v>
       </c>
-      <c r="J36" s="1">
-        <v>0</v>
+      <c r="J36" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M36" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N36" s="1">
-        <v>2008</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>0</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V36" s="1">
-        <v>30</v>
-      </c>
-      <c r="W36" s="1">
-        <v>100</v>
-      </c>
-      <c r="X36" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:14">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>108</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4190,68 +2858,35 @@
         <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I37" s="1">
         <v>1933</v>
       </c>
-      <c r="J37" s="1">
-        <v>0</v>
+      <c r="J37" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M37" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N37" s="1">
-        <v>2009</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R37" s="1">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1">
-        <v>0</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V37" s="1">
-        <v>30</v>
-      </c>
-      <c r="W37" s="1">
-        <v>100</v>
-      </c>
-      <c r="X37" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:14">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>109</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4263,68 +2898,35 @@
         <v>0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="I38" s="1">
         <v>1934</v>
       </c>
-      <c r="J38" s="1">
-        <v>0</v>
+      <c r="J38" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M38" s="1">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="N38" s="1">
-        <v>2010</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V38" s="1">
-        <v>100</v>
-      </c>
-      <c r="W38" s="1">
-        <v>800</v>
-      </c>
-      <c r="X38" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:14">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>110</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4336,68 +2938,35 @@
         <v>0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="I39" s="1">
         <v>1935</v>
       </c>
-      <c r="J39" s="1">
-        <v>0</v>
+      <c r="J39" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M39" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N39" s="1">
-        <v>2011</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1">
-        <v>0</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V39" s="1">
-        <v>50</v>
-      </c>
-      <c r="W39" s="1">
-        <v>300</v>
-      </c>
-      <c r="X39" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:14">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>111</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4409,68 +2978,35 @@
         <v>0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="I40" s="1">
         <v>1936</v>
       </c>
-      <c r="J40" s="1">
-        <v>0</v>
+      <c r="J40" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M40" s="1">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="N40" s="1">
-        <v>2012</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1">
-        <v>0</v>
-      </c>
-      <c r="T40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V40" s="1">
-        <v>100</v>
-      </c>
-      <c r="W40" s="1">
-        <v>800</v>
-      </c>
-      <c r="X40" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:14">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>112</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4482,68 +3018,35 @@
         <v>0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="I41" s="1">
         <v>1937</v>
       </c>
-      <c r="J41" s="1">
-        <v>0</v>
+      <c r="J41" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M41" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N41" s="1">
-        <v>2013</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R41" s="1">
-        <v>0</v>
-      </c>
-      <c r="S41" s="1">
-        <v>0</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V41" s="1">
-        <v>30</v>
-      </c>
-      <c r="W41" s="1">
-        <v>100</v>
-      </c>
-      <c r="X41" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:14">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>113</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4555,68 +3058,35 @@
         <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="I42" s="1">
         <v>1938</v>
       </c>
-      <c r="J42" s="1">
-        <v>0</v>
+      <c r="J42" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M42" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N42" s="1">
-        <v>2014</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V42" s="1">
-        <v>50</v>
-      </c>
-      <c r="W42" s="1">
-        <v>300</v>
-      </c>
-      <c r="X42" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:14">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>114</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -4628,68 +3098,35 @@
         <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="I43" s="1">
         <v>1939</v>
       </c>
-      <c r="J43" s="1">
-        <v>0</v>
+      <c r="J43" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M43" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N43" s="1">
-        <v>2015</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-      <c r="P43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V43" s="1">
-        <v>50</v>
-      </c>
-      <c r="W43" s="1">
-        <v>300</v>
-      </c>
-      <c r="X43" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:14">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>115</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4701,68 +3138,35 @@
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="I44" s="1">
         <v>1940</v>
       </c>
-      <c r="J44" s="1">
-        <v>0</v>
+      <c r="J44" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
       </c>
       <c r="L44" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M44" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N44" s="1">
-        <v>2016</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V44" s="1">
-        <v>50</v>
-      </c>
-      <c r="W44" s="1">
-        <v>300</v>
-      </c>
-      <c r="X44" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:14">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>116</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4774,68 +3178,35 @@
         <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="I45" s="1">
         <v>1941</v>
       </c>
-      <c r="J45" s="1">
-        <v>0</v>
+      <c r="J45" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
       <c r="L45" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M45" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N45" s="1">
-        <v>2017</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-      <c r="S45" s="1">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V45" s="1">
-        <v>50</v>
-      </c>
-      <c r="W45" s="1">
-        <v>300</v>
-      </c>
-      <c r="X45" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:14">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>117</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -4847,68 +3218,35 @@
         <v>0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="I46" s="1">
         <v>1942</v>
       </c>
-      <c r="J46" s="1">
-        <v>0</v>
+      <c r="J46" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K46" s="1">
         <v>1</v>
       </c>
       <c r="L46" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M46" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N46" s="1">
-        <v>2018</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V46" s="1">
-        <v>50</v>
-      </c>
-      <c r="W46" s="1">
-        <v>300</v>
-      </c>
-      <c r="X46" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:14">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>118</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4920,68 +3258,35 @@
         <v>0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="I47" s="1">
         <v>1943</v>
       </c>
-      <c r="J47" s="1">
-        <v>0</v>
+      <c r="J47" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
       <c r="L47" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M47" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N47" s="1">
-        <v>2019</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V47" s="1">
-        <v>50</v>
-      </c>
-      <c r="W47" s="1">
-        <v>300</v>
-      </c>
-      <c r="X47" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="1:14">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>119</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4993,68 +3298,35 @@
         <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="I48" s="1">
         <v>1944</v>
       </c>
-      <c r="J48" s="1">
-        <v>0</v>
+      <c r="J48" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
       <c r="L48" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M48" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N48" s="1">
-        <v>2020</v>
-      </c>
-      <c r="O48" s="1">
-        <v>0</v>
-      </c>
-      <c r="P48" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R48" s="1">
-        <v>0</v>
-      </c>
-      <c r="S48" s="1">
-        <v>0</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V48" s="1">
-        <v>50</v>
-      </c>
-      <c r="W48" s="1">
-        <v>300</v>
-      </c>
-      <c r="X48" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:14">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>120</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -5066,68 +3338,35 @@
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="I49" s="1">
         <v>1945</v>
       </c>
-      <c r="J49" s="1">
-        <v>0</v>
+      <c r="J49" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K49" s="1">
         <v>1</v>
       </c>
       <c r="L49" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M49" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N49" s="1">
-        <v>2021</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V49" s="1">
-        <v>30</v>
-      </c>
-      <c r="W49" s="1">
-        <v>100</v>
-      </c>
-      <c r="X49" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" spans="1:14">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>121</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -5139,68 +3378,35 @@
         <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="I50" s="1">
         <v>1946</v>
       </c>
-      <c r="J50" s="1">
-        <v>0</v>
+      <c r="J50" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K50" s="1">
         <v>1</v>
       </c>
       <c r="L50" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M50" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="N50" s="1">
-        <v>2022</v>
-      </c>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U50" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V50" s="1">
-        <v>50</v>
-      </c>
-      <c r="W50" s="1">
-        <v>300</v>
-      </c>
-      <c r="X50" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" spans="1:14">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>122</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -5212,68 +3418,35 @@
         <v>0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="I51" s="1">
         <v>1947</v>
       </c>
-      <c r="J51" s="1">
-        <v>0</v>
+      <c r="J51" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K51" s="1">
         <v>1</v>
       </c>
       <c r="L51" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M51" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N51" s="1">
-        <v>2023</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V51" s="1">
-        <v>30</v>
-      </c>
-      <c r="W51" s="1">
-        <v>100</v>
-      </c>
-      <c r="X51" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" spans="1:14">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>123</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -5285,68 +3458,35 @@
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="I52" s="1">
         <v>1948</v>
       </c>
-      <c r="J52" s="1">
-        <v>0</v>
+      <c r="J52" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M52" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N52" s="1">
-        <v>2024</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V52" s="1">
-        <v>30</v>
-      </c>
-      <c r="W52" s="1">
-        <v>100</v>
-      </c>
-      <c r="X52" s="1">
-        <v>50</v>
-      </c>
-      <c r="Y52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" spans="1:25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:14">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>999</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="E53" s="1">
         <v>5</v>
@@ -5358,68 +3498,35 @@
         <v>0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="I53" s="1">
         <v>1101</v>
       </c>
-      <c r="J53" s="1">
-        <v>0</v>
+      <c r="J53" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K53" s="1">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="L53" s="1">
-        <v>999999999</v>
+        <v>0</v>
       </c>
       <c r="M53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" s="1">
         <v>0</v>
       </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V53" s="1">
-        <v>0</v>
-      </c>
-      <c r="W53" s="1">
-        <v>1</v>
-      </c>
-      <c r="X53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="1:14">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>9999</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="E54" s="1">
         <v>5</v>
@@ -5431,68 +3538,35 @@
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="I54" s="1">
         <v>1102</v>
       </c>
-      <c r="J54" s="1">
-        <v>0</v>
+      <c r="J54" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K54" s="1">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="L54" s="1">
-        <v>999999999</v>
+        <v>0</v>
       </c>
       <c r="M54" s="1">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="N54" s="1">
         <v>0</v>
       </c>
-      <c r="O54" s="1">
-        <v>0</v>
-      </c>
-      <c r="P54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-      <c r="S54" s="1">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V54" s="1">
-        <v>0</v>
-      </c>
-      <c r="W54" s="1">
-        <v>999</v>
-      </c>
-      <c r="X54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="1:25">
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:14">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>99999</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="E55" s="1">
         <v>5</v>
@@ -5504,57 +3578,24 @@
         <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="I55" s="1">
         <v>1103</v>
       </c>
-      <c r="J55" s="1">
-        <v>0</v>
+      <c r="J55" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="K55" s="1">
-        <v>1</v>
+        <v>999999999</v>
       </c>
       <c r="L55" s="1">
-        <v>999999999</v>
+        <v>0</v>
       </c>
       <c r="M55" s="1">
         <v>0</v>
       </c>
       <c r="N55" s="1">
-        <v>0</v>
-      </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V55" s="1">
-        <v>0</v>
-      </c>
-      <c r="W55" s="1">
-        <v>0</v>
-      </c>
-      <c r="X55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="1">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/ItemTable.xlsx
+++ b/AAAGameData/DataTables/ItemTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -435,14 +435,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,148 +891,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1395,7 +1388,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
